--- a/Datasets_Catalogue.xlsx
+++ b/Datasets_Catalogue.xlsx
@@ -5313,7 +5313,7 @@
     <t xml:space="preserve">ABC</t>
   </si>
   <si>
-    <t xml:space="preserve">27-65 (48.8 pm 9.9)</t>
+    <t xml:space="preserve">27-65 (48.8±9.9)</t>
   </si>
   <si>
     <t xml:space="preserve">28/21</t>
@@ -8447,7 +8447,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="131">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8912,6 +8912,10 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="0" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -33419,19 +33423,19 @@
       <c r="G78" s="89" t="s">
         <v>2343</v>
       </c>
-      <c r="H78" s="89" t="s">
+      <c r="H78" s="116" t="s">
         <v>2344</v>
       </c>
       <c r="I78" s="90" t="s">
         <v>2345</v>
       </c>
-      <c r="J78" s="116" t="s">
+      <c r="J78" s="117" t="s">
         <v>2346</v>
       </c>
-      <c r="K78" s="116" t="s">
+      <c r="K78" s="117" t="s">
         <v>2346</v>
       </c>
-      <c r="L78" s="117" t="s">
+      <c r="L78" s="118" t="s">
         <v>2346</v>
       </c>
       <c r="M78" s="89" t="s">
@@ -33560,7 +33564,7 @@
       <c r="J80" s="89" t="s">
         <v>2354</v>
       </c>
-      <c r="K80" s="118" t="s">
+      <c r="K80" s="119" t="s">
         <v>2355</v>
       </c>
       <c r="L80" s="90" t="s">
@@ -34043,7 +34047,7 @@
       <c r="AK86" s="104" t="s">
         <v>2404</v>
       </c>
-      <c r="AL86" s="119" t="s">
+      <c r="AL86" s="120" t="s">
         <v>2405</v>
       </c>
       <c r="AM86" s="91" t="s">
@@ -34462,7 +34466,7 @@
       <c r="AJ94" s="89" t="s">
         <v>2449</v>
       </c>
-      <c r="AK94" s="120" t="s">
+      <c r="AK94" s="121" t="s">
         <v>2450</v>
       </c>
       <c r="AL94" s="91" t="s">
@@ -34615,7 +34619,7 @@
       <c r="B97" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C97" s="121" t="s">
+      <c r="C97" s="122" t="s">
         <v>2472</v>
       </c>
       <c r="D97" s="111" t="s">
@@ -34657,7 +34661,7 @@
       <c r="AK97" s="90" t="s">
         <v>2483</v>
       </c>
-      <c r="AL97" s="122" t="s">
+      <c r="AL97" s="123" t="s">
         <v>2484</v>
       </c>
       <c r="AO97" s="9"/>
@@ -34710,7 +34714,7 @@
       <c r="AK98" s="90" t="s">
         <v>2494</v>
       </c>
-      <c r="AL98" s="122" t="s">
+      <c r="AL98" s="123" t="s">
         <v>2495</v>
       </c>
       <c r="AO98" s="9"/>
@@ -35107,7 +35111,7 @@
       <c r="AP105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="123" t="s">
+      <c r="A106" s="124" t="s">
         <v>2542</v>
       </c>
       <c r="B106" s="1" t="n">
@@ -35191,31 +35195,31 @@
       <c r="AB106" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC106" s="124" t="s">
+      <c r="AC106" s="125" t="s">
         <v>2546</v>
       </c>
-      <c r="AD106" s="124" t="s">
+      <c r="AD106" s="125" t="s">
         <v>2547</v>
       </c>
-      <c r="AE106" s="124" t="s">
+      <c r="AE106" s="125" t="s">
         <v>2548</v>
       </c>
-      <c r="AF106" s="124" t="s">
+      <c r="AF106" s="125" t="s">
         <v>2549</v>
       </c>
-      <c r="AG106" s="124" t="s">
+      <c r="AG106" s="125" t="s">
         <v>2550</v>
       </c>
-      <c r="AH106" s="124" t="s">
+      <c r="AH106" s="125" t="s">
         <v>2551</v>
       </c>
-      <c r="AI106" s="124" t="s">
+      <c r="AI106" s="125" t="s">
         <v>2552</v>
       </c>
-      <c r="AJ106" s="124" t="s">
+      <c r="AJ106" s="125" t="s">
         <v>2553</v>
       </c>
-      <c r="AK106" s="125" t="s">
+      <c r="AK106" s="126" t="s">
         <v>2554</v>
       </c>
       <c r="AL106" s="4" t="s">
@@ -35978,7 +35982,7 @@
       <c r="H124" s="27" t="n">
         <v>52</v>
       </c>
-      <c r="I124" s="126" t="n">
+      <c r="I124" s="127" t="n">
         <v>12.4</v>
       </c>
       <c r="J124" s="27" t="n">
@@ -36001,7 +36005,7 @@
       <c r="H125" s="27" t="n">
         <v>57</v>
       </c>
-      <c r="I125" s="126" t="n">
+      <c r="I125" s="127" t="n">
         <v>9.1</v>
       </c>
       <c r="J125" s="27"/>
@@ -36018,7 +36022,7 @@
       <c r="H126" s="27" t="n">
         <v>59</v>
       </c>
-      <c r="I126" s="126" t="n">
+      <c r="I126" s="127" t="n">
         <v>19.6</v>
       </c>
       <c r="L126" s="3"/>
@@ -36031,7 +36035,7 @@
       <c r="H127" s="27" t="n">
         <v>55</v>
       </c>
-      <c r="I127" s="126"/>
+      <c r="I127" s="127"/>
       <c r="J127" s="27"/>
       <c r="L127" s="3"/>
     </row>
@@ -36044,7 +36048,7 @@
       <c r="H128" s="27" t="n">
         <v>57</v>
       </c>
-      <c r="I128" s="126"/>
+      <c r="I128" s="127"/>
       <c r="L128" s="3"/>
     </row>
     <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36052,66 +36056,66 @@
       <c r="E129" s="89"/>
       <c r="G129" s="27"/>
       <c r="H129" s="27"/>
-      <c r="I129" s="126"/>
+      <c r="I129" s="127"/>
     </row>
     <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D130" s="89"/>
       <c r="E130" s="89"/>
       <c r="G130" s="27"/>
       <c r="H130" s="27"/>
-      <c r="I130" s="126"/>
+      <c r="I130" s="127"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D131" s="89"/>
       <c r="G131" s="27"/>
       <c r="H131" s="27"/>
-      <c r="I131" s="126"/>
+      <c r="I131" s="127"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D132" s="89"/>
       <c r="G132" s="27"/>
       <c r="H132" s="27"/>
-      <c r="I132" s="126"/>
+      <c r="I132" s="127"/>
     </row>
     <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G133" s="27"/>
       <c r="H133" s="27"/>
-      <c r="I133" s="126"/>
+      <c r="I133" s="127"/>
     </row>
     <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G134" s="27"/>
       <c r="H134" s="27"/>
-      <c r="I134" s="126"/>
+      <c r="I134" s="127"/>
     </row>
     <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G135" s="27"/>
       <c r="H135" s="27"/>
-      <c r="I135" s="126"/>
+      <c r="I135" s="127"/>
     </row>
     <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G136" s="27"/>
       <c r="H136" s="27"/>
-      <c r="I136" s="126"/>
+      <c r="I136" s="127"/>
     </row>
     <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G137" s="27"/>
       <c r="H137" s="27"/>
-      <c r="I137" s="126"/>
+      <c r="I137" s="127"/>
     </row>
     <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G138" s="27"/>
       <c r="H138" s="27"/>
-      <c r="I138" s="126"/>
+      <c r="I138" s="127"/>
     </row>
     <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G139" s="27"/>
       <c r="H139" s="27"/>
-      <c r="I139" s="126"/>
+      <c r="I139" s="127"/>
     </row>
     <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G140" s="27"/>
       <c r="H140" s="27"/>
-      <c r="I140" s="126"/>
+      <c r="I140" s="127"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
@@ -36166,46 +36170,46 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="27" style="89" width="10.91"/>
   </cols>
   <sheetData>
-    <row r="1" s="127" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B1" s="128" t="s">
+    <row r="1" s="128" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B1" s="129" t="s">
         <v>2649</v>
       </c>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128" t="s">
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129" t="s">
         <v>2650</v>
       </c>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="128"/>
-      <c r="I1" s="128" t="s">
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="I1" s="129" t="s">
         <v>2651</v>
       </c>
-      <c r="J1" s="128"/>
-      <c r="K1" s="128"/>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128" t="s">
+      <c r="J1" s="129"/>
+      <c r="K1" s="129"/>
+      <c r="L1" s="129"/>
+      <c r="M1" s="129"/>
+      <c r="N1" s="129" t="s">
         <v>2652</v>
       </c>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128" t="s">
+      <c r="O1" s="129"/>
+      <c r="P1" s="129"/>
+      <c r="Q1" s="129" t="s">
         <v>1154</v>
       </c>
-      <c r="R1" s="128"/>
-      <c r="S1" s="128"/>
-      <c r="T1" s="128"/>
-      <c r="U1" s="128"/>
-      <c r="V1" s="128" t="s">
+      <c r="R1" s="129"/>
+      <c r="S1" s="129"/>
+      <c r="T1" s="129"/>
+      <c r="U1" s="129"/>
+      <c r="V1" s="129" t="s">
         <v>2653</v>
       </c>
-      <c r="W1" s="128"/>
-      <c r="X1" s="128" t="s">
+      <c r="W1" s="129"/>
+      <c r="X1" s="129" t="s">
         <v>2654</v>
       </c>
-      <c r="Y1" s="128"/>
-      <c r="Z1" s="128"/>
+      <c r="Y1" s="129"/>
+      <c r="Z1" s="129"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="93" t="s">
@@ -37573,7 +37577,7 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="124" t="s">
+      <c r="A44" s="125" t="s">
         <v>2542</v>
       </c>
       <c r="B44" s="89" t="s">
@@ -37622,64 +37626,64 @@
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="129" t="s">
+      <c r="A55" s="130" t="s">
         <v>2699</v>
       </c>
-      <c r="B55" s="129"/>
-      <c r="C55" s="129"/>
-      <c r="D55" s="129"/>
-      <c r="E55" s="129"/>
-      <c r="F55" s="129"/>
-      <c r="G55" s="129"/>
-      <c r="H55" s="129"/>
-      <c r="I55" s="129"/>
-      <c r="J55" s="129"/>
-      <c r="K55" s="129"/>
-      <c r="L55" s="129"/>
+      <c r="B55" s="130"/>
+      <c r="C55" s="130"/>
+      <c r="D55" s="130"/>
+      <c r="E55" s="130"/>
+      <c r="F55" s="130"/>
+      <c r="G55" s="130"/>
+      <c r="H55" s="130"/>
+      <c r="I55" s="130"/>
+      <c r="J55" s="130"/>
+      <c r="K55" s="130"/>
+      <c r="L55" s="130"/>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="129" t="s">
+      <c r="A56" s="130" t="s">
         <v>2700</v>
       </c>
-      <c r="B56" s="129"/>
-      <c r="C56" s="129"/>
-      <c r="D56" s="129"/>
-      <c r="E56" s="129"/>
-      <c r="F56" s="129"/>
-      <c r="G56" s="129"/>
-      <c r="H56" s="129"/>
-      <c r="I56" s="129"/>
-      <c r="J56" s="129"/>
-      <c r="K56" s="129"/>
+      <c r="B56" s="130"/>
+      <c r="C56" s="130"/>
+      <c r="D56" s="130"/>
+      <c r="E56" s="130"/>
+      <c r="F56" s="130"/>
+      <c r="G56" s="130"/>
+      <c r="H56" s="130"/>
+      <c r="I56" s="130"/>
+      <c r="J56" s="130"/>
+      <c r="K56" s="130"/>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="129" t="s">
+      <c r="A57" s="130" t="s">
         <v>2701</v>
       </c>
-      <c r="B57" s="129"/>
-      <c r="C57" s="129"/>
-      <c r="D57" s="129"/>
-      <c r="E57" s="129"/>
-      <c r="F57" s="129"/>
-      <c r="G57" s="129"/>
-      <c r="H57" s="129"/>
-      <c r="I57" s="129"/>
-      <c r="J57" s="129"/>
-      <c r="K57" s="129"/>
+      <c r="B57" s="130"/>
+      <c r="C57" s="130"/>
+      <c r="D57" s="130"/>
+      <c r="E57" s="130"/>
+      <c r="F57" s="130"/>
+      <c r="G57" s="130"/>
+      <c r="H57" s="130"/>
+      <c r="I57" s="130"/>
+      <c r="J57" s="130"/>
+      <c r="K57" s="130"/>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="129" t="s">
+      <c r="A58" s="130" t="s">
         <v>2702</v>
       </c>
-      <c r="B58" s="129"/>
-      <c r="C58" s="129"/>
-      <c r="D58" s="129"/>
-      <c r="E58" s="129"/>
-      <c r="F58" s="129"/>
-      <c r="G58" s="129"/>
-      <c r="H58" s="129"/>
-      <c r="I58" s="129"/>
-      <c r="J58" s="129"/>
+      <c r="B58" s="130"/>
+      <c r="C58" s="130"/>
+      <c r="D58" s="130"/>
+      <c r="E58" s="130"/>
+      <c r="F58" s="130"/>
+      <c r="G58" s="130"/>
+      <c r="H58" s="130"/>
+      <c r="I58" s="130"/>
+      <c r="J58" s="130"/>
     </row>
   </sheetData>
   <mergeCells count="11">

--- a/Datasets_Catalogue.xlsx
+++ b/Datasets_Catalogue.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7619" uniqueCount="2740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7617" uniqueCount="2745">
   <si>
     <t xml:space="preserve">Meta data</t>
   </si>
@@ -7606,172 +7606,28 @@
     <t xml:space="preserve">424.4±123.6</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">315</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">.2±129.5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">73.6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±22.4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">38.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±69.5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">69.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±79.4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">13.3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±12.9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">58.2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±18.1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10.0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±10.6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">18.5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">±14.2</t>
-    </r>
+    <t xml:space="preserve">315.2±129.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.6±22.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.3±69.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">69.3±79.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3±12.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.2±18.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0±10.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5±14.2</t>
   </si>
   <si>
     <t xml:space="preserve">special/clinical population: adult and adolescent patients who were evaluated for sleep disorders at sleep clinics, making it a help-seeking clinical cohort rather than a population-based or healthy control sample</t>
@@ -8212,7 +8068,22 @@
     <t xml:space="preserve">32-56</t>
   </si>
   <si>
+    <t xml:space="preserve">BERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4626/5258</t>
+  </si>
+  <si>
     <t xml:space="preserve">16.7±24.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2765/3039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1861/2219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">824/944</t>
   </si>
   <si>
     <t xml:space="preserve">14.5±4.0</t>
@@ -8412,7 +8283,7 @@
     <numFmt numFmtId="170" formatCode="@"/>
     <numFmt numFmtId="171" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8490,12 +8361,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -31713,94 +31578,36 @@
       <c r="AP41" s="9"/>
       <c r="AQ41" s="35"/>
     </row>
-    <row r="42" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="87" t="s">
         <v>2086</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="89"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="90"/>
-      <c r="M42" s="89"/>
-      <c r="N42" s="89"/>
-      <c r="O42" s="89"/>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="89"/>
-      <c r="R42" s="89"/>
-      <c r="S42" s="89"/>
-      <c r="T42" s="89"/>
-      <c r="U42" s="89"/>
-      <c r="V42" s="89"/>
-      <c r="W42" s="89"/>
-      <c r="X42" s="89"/>
-      <c r="Y42" s="89"/>
-      <c r="Z42" s="89"/>
-      <c r="AA42" s="89"/>
-      <c r="AB42" s="90"/>
-      <c r="AC42" s="89"/>
-      <c r="AD42" s="89"/>
-      <c r="AE42" s="89"/>
-      <c r="AF42" s="89"/>
-      <c r="AG42" s="89"/>
-      <c r="AH42" s="89"/>
-      <c r="AI42" s="89"/>
-      <c r="AJ42" s="89"/>
-      <c r="AK42" s="90"/>
-      <c r="AL42" s="91"/>
-      <c r="AM42" s="91"/>
+      <c r="D42" s="1"/>
       <c r="AO42" s="111"/>
       <c r="AP42" s="9"/>
       <c r="AQ42" s="35"/>
-    </row>
-    <row r="43" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AU42" s="1"/>
+      <c r="AV42" s="1"/>
+      <c r="AW42" s="1"/>
+      <c r="AX42" s="1"/>
+      <c r="AY42" s="1"/>
+      <c r="AZ42" s="1"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="87"/>
-      <c r="C43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="90"/>
-      <c r="J43" s="89"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="90"/>
-      <c r="M43" s="89"/>
-      <c r="N43" s="89"/>
-      <c r="O43" s="89"/>
-      <c r="P43" s="89"/>
-      <c r="Q43" s="89"/>
-      <c r="R43" s="89"/>
-      <c r="S43" s="89"/>
-      <c r="T43" s="89"/>
-      <c r="U43" s="89"/>
-      <c r="V43" s="89"/>
-      <c r="W43" s="89"/>
-      <c r="X43" s="89"/>
-      <c r="Y43" s="89"/>
-      <c r="Z43" s="89"/>
-      <c r="AA43" s="89"/>
-      <c r="AB43" s="90"/>
-      <c r="AC43" s="89"/>
-      <c r="AD43" s="89"/>
-      <c r="AE43" s="89"/>
-      <c r="AF43" s="89"/>
-      <c r="AG43" s="89"/>
-      <c r="AH43" s="89"/>
-      <c r="AI43" s="89"/>
-      <c r="AJ43" s="89"/>
-      <c r="AK43" s="90"/>
-      <c r="AL43" s="91"/>
-      <c r="AM43" s="91"/>
+      <c r="D43" s="1"/>
       <c r="AO43" s="111"/>
       <c r="AP43" s="9"/>
       <c r="AQ43" s="35"/>
+      <c r="AU43" s="1"/>
+      <c r="AV43" s="1"/>
+      <c r="AW43" s="1"/>
+      <c r="AX43" s="1"/>
+      <c r="AY43" s="1"/>
+      <c r="AZ43" s="1"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="99" t="s">
@@ -35105,7 +34912,7 @@
       <c r="AO101" s="9"/>
       <c r="AP101" s="2"/>
     </row>
-    <row r="102" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="99" t="s">
         <v>1684</v>
       </c>
@@ -39510,143 +39317,179 @@
       <c r="AP41" s="9"/>
       <c r="AQ41" s="35"/>
     </row>
-    <row r="42" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="87" t="s">
-        <v>2086</v>
+    <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="99" t="s">
+        <v>2087</v>
       </c>
       <c r="B42" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="90"/>
-      <c r="J42" s="89"/>
-      <c r="K42" s="89"/>
-      <c r="L42" s="90"/>
-      <c r="M42" s="89"/>
-      <c r="N42" s="89"/>
-      <c r="O42" s="89"/>
-      <c r="P42" s="89"/>
-      <c r="Q42" s="89"/>
-      <c r="R42" s="89"/>
-      <c r="S42" s="89"/>
-      <c r="T42" s="89"/>
-      <c r="U42" s="89"/>
-      <c r="V42" s="89"/>
-      <c r="W42" s="89"/>
-      <c r="X42" s="89"/>
-      <c r="Y42" s="89"/>
-      <c r="Z42" s="89"/>
-      <c r="AA42" s="89"/>
-      <c r="AB42" s="90"/>
-      <c r="AC42" s="89"/>
-      <c r="AD42" s="89"/>
-      <c r="AE42" s="89"/>
-      <c r="AF42" s="89"/>
-      <c r="AG42" s="89"/>
-      <c r="AH42" s="89"/>
-      <c r="AI42" s="89"/>
-      <c r="AJ42" s="89"/>
-      <c r="AK42" s="90"/>
-      <c r="AL42" s="91"/>
-      <c r="AM42" s="91"/>
-      <c r="AO42" s="111"/>
+      <c r="C42" s="27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="E42" s="100" t="n">
+        <v>151</v>
+      </c>
+      <c r="F42" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="89" t="s">
+        <v>2088</v>
+      </c>
+      <c r="H42" s="89" t="s">
+        <v>460</v>
+      </c>
+      <c r="I42" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="J42" s="89" t="s">
+        <v>2089</v>
+      </c>
+      <c r="K42" s="89" t="s">
+        <v>2090</v>
+      </c>
+      <c r="L42" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="M42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z42" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB42" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC42" s="101" t="s">
+        <v>2091</v>
+      </c>
+      <c r="AD42" s="101" t="s">
+        <v>2092</v>
+      </c>
+      <c r="AE42" s="101" t="s">
+        <v>2093</v>
+      </c>
+      <c r="AF42" s="89" t="s">
+        <v>2094</v>
+      </c>
+      <c r="AG42" s="89" t="s">
+        <v>2095</v>
+      </c>
+      <c r="AH42" s="89" t="s">
+        <v>2096</v>
+      </c>
+      <c r="AI42" s="89" t="s">
+        <v>2097</v>
+      </c>
+      <c r="AJ42" s="89" t="s">
+        <v>2098</v>
+      </c>
+      <c r="AK42" s="90" t="s">
+        <v>2099</v>
+      </c>
+      <c r="AL42" s="4" t="s">
+        <v>2100</v>
+      </c>
+      <c r="AM42" s="91" t="s">
+        <v>1791</v>
+      </c>
       <c r="AP42" s="9"/>
-      <c r="AQ42" s="35"/>
-    </row>
-    <row r="43" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AQ42" s="14"/>
+    </row>
+    <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="87"/>
-      <c r="C43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="90"/>
-      <c r="J43" s="89"/>
-      <c r="K43" s="89"/>
-      <c r="L43" s="90"/>
-      <c r="M43" s="89"/>
-      <c r="N43" s="89"/>
-      <c r="O43" s="89"/>
-      <c r="P43" s="89"/>
-      <c r="Q43" s="89"/>
-      <c r="R43" s="89"/>
-      <c r="S43" s="89"/>
-      <c r="T43" s="89"/>
-      <c r="U43" s="89"/>
-      <c r="V43" s="89"/>
-      <c r="W43" s="89"/>
-      <c r="X43" s="89"/>
-      <c r="Y43" s="89"/>
-      <c r="Z43" s="89"/>
-      <c r="AA43" s="89"/>
-      <c r="AB43" s="90"/>
-      <c r="AC43" s="89"/>
-      <c r="AD43" s="89"/>
-      <c r="AE43" s="89"/>
-      <c r="AF43" s="89"/>
-      <c r="AG43" s="89"/>
-      <c r="AH43" s="89"/>
-      <c r="AI43" s="89"/>
-      <c r="AJ43" s="89"/>
-      <c r="AK43" s="90"/>
-      <c r="AL43" s="91"/>
-      <c r="AM43" s="91"/>
-      <c r="AO43" s="111"/>
+      <c r="D43" s="1"/>
+      <c r="AC43" s="103"/>
+      <c r="AD43" s="103"/>
+      <c r="AE43" s="103"/>
+      <c r="AL43" s="4"/>
       <c r="AP43" s="9"/>
-      <c r="AQ43" s="35"/>
+      <c r="AQ43" s="14"/>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="99" t="s">
-        <v>2087</v>
+      <c r="A44" s="107" t="s">
+        <v>2103</v>
       </c>
       <c r="B44" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C44" s="27" t="n">
-        <v>2018</v>
+      <c r="C44" s="27" t="s">
+        <v>468</v>
       </c>
       <c r="D44" s="1" t="n">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="E44" s="100" t="n">
-        <v>151</v>
+        <v>411</v>
       </c>
       <c r="F44" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G44" s="89" t="s">
-        <v>2088</v>
+        <v>2105</v>
       </c>
       <c r="H44" s="89" t="s">
-        <v>460</v>
+        <v>2106</v>
       </c>
       <c r="I44" s="90" t="s">
-        <v>84</v>
+        <v>2107</v>
       </c>
       <c r="J44" s="89" t="s">
-        <v>2089</v>
+        <v>2108</v>
       </c>
       <c r="K44" s="89" t="s">
-        <v>2090</v>
+        <v>84</v>
       </c>
       <c r="L44" s="90" t="s">
         <v>84</v>
       </c>
       <c r="M44" s="89" t="s">
-        <v>84</v>
+        <v>2109</v>
       </c>
       <c r="N44" s="89" t="s">
         <v>84</v>
       </c>
       <c r="O44" s="89" t="s">
-        <v>84</v>
+        <v>2110</v>
       </c>
       <c r="P44" s="89" t="s">
-        <v>84</v>
+        <v>2111</v>
       </c>
       <c r="Q44" s="89" t="s">
         <v>84</v>
@@ -39658,7 +39501,7 @@
         <v>84</v>
       </c>
       <c r="T44" s="89" t="s">
-        <v>84</v>
+        <v>2112</v>
       </c>
       <c r="U44" s="89" t="s">
         <v>84</v>
@@ -39673,328 +39516,371 @@
         <v>84</v>
       </c>
       <c r="Z44" s="89" t="s">
-        <v>84</v>
+        <v>2113</v>
       </c>
       <c r="AB44" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC44" s="101" t="s">
-        <v>2091</v>
+      <c r="AC44" s="89" t="s">
+        <v>2114</v>
       </c>
       <c r="AD44" s="101" t="s">
-        <v>2092</v>
-      </c>
-      <c r="AE44" s="101" t="s">
-        <v>2093</v>
+        <v>2115</v>
+      </c>
+      <c r="AE44" s="89" t="s">
+        <v>2116</v>
       </c>
       <c r="AF44" s="89" t="s">
-        <v>2094</v>
+        <v>2117</v>
       </c>
       <c r="AG44" s="89" t="s">
-        <v>2095</v>
-      </c>
-      <c r="AH44" s="89" t="s">
-        <v>2096</v>
+        <v>2118</v>
+      </c>
+      <c r="AH44" s="101" t="s">
+        <v>2119</v>
       </c>
       <c r="AI44" s="89" t="s">
-        <v>2097</v>
+        <v>2120</v>
       </c>
       <c r="AJ44" s="89" t="s">
-        <v>2098</v>
-      </c>
-      <c r="AK44" s="90" t="s">
-        <v>2099</v>
-      </c>
-      <c r="AL44" s="4" t="s">
-        <v>2100</v>
+        <v>2121</v>
+      </c>
+      <c r="AK44" s="101" t="s">
+        <v>2122</v>
+      </c>
+      <c r="AL44" s="91" t="s">
+        <v>2123</v>
       </c>
       <c r="AM44" s="91" t="s">
-        <v>1791</v>
+        <v>1775</v>
       </c>
       <c r="AP44" s="9"/>
-      <c r="AQ44" s="14"/>
+      <c r="AQ44" s="35"/>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="87"/>
       <c r="D45" s="1"/>
-      <c r="AC45" s="103"/>
-      <c r="AD45" s="103"/>
-      <c r="AE45" s="103"/>
-      <c r="AL45" s="4"/>
       <c r="AP45" s="9"/>
-      <c r="AQ45" s="14"/>
+      <c r="AQ45" s="35"/>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="107" t="s">
-        <v>2103</v>
+      <c r="A46" s="99" t="s">
+        <v>481</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="27" t="s">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="D46" s="1" t="n">
-        <v>197</v>
-      </c>
-      <c r="E46" s="100" t="n">
-        <v>411</v>
+        <v>118</v>
+      </c>
+      <c r="E46" s="101" t="s">
+        <v>2126</v>
       </c>
       <c r="F46" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G46" s="89" t="s">
-        <v>2105</v>
-      </c>
-      <c r="H46" s="89" t="s">
-        <v>2106</v>
-      </c>
-      <c r="I46" s="90" t="s">
-        <v>2107</v>
-      </c>
-      <c r="J46" s="89" t="s">
-        <v>2108</v>
-      </c>
-      <c r="K46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L46" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="M46" s="89" t="s">
-        <v>2109</v>
-      </c>
-      <c r="N46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O46" s="89" t="s">
-        <v>2110</v>
-      </c>
-      <c r="P46" s="89" t="s">
-        <v>2111</v>
-      </c>
-      <c r="Q46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="S46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T46" s="89" t="s">
-        <v>2112</v>
-      </c>
-      <c r="U46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y46" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z46" s="89" t="s">
-        <v>2113</v>
-      </c>
-      <c r="AB46" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC46" s="89" t="s">
-        <v>2114</v>
+        <v>2127</v>
+      </c>
+      <c r="H46" s="112" t="s">
+        <v>2128</v>
+      </c>
+      <c r="I46" s="113" t="s">
+        <v>2669</v>
+      </c>
+      <c r="J46" s="27" t="s">
+        <v>2130</v>
+      </c>
+      <c r="K46" s="27" t="s">
+        <v>2131</v>
+      </c>
+      <c r="L46" s="112" t="s">
+        <v>2132</v>
+      </c>
+      <c r="M46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="N46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="O46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="P46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="R46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="S46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="T46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="U46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="V46" s="27"/>
+      <c r="W46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="X46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z46" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA46" s="27"/>
+      <c r="AB46" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC46" s="101" t="s">
+        <v>2133</v>
       </c>
       <c r="AD46" s="101" t="s">
-        <v>2115</v>
-      </c>
-      <c r="AE46" s="89" t="s">
-        <v>2116</v>
-      </c>
-      <c r="AF46" s="89" t="s">
-        <v>2117</v>
-      </c>
-      <c r="AG46" s="89" t="s">
-        <v>2118</v>
-      </c>
-      <c r="AH46" s="101" t="s">
-        <v>2119</v>
-      </c>
-      <c r="AI46" s="89" t="s">
-        <v>2120</v>
-      </c>
-      <c r="AJ46" s="89" t="s">
-        <v>2121</v>
-      </c>
-      <c r="AK46" s="101" t="s">
-        <v>2122</v>
-      </c>
-      <c r="AL46" s="91" t="s">
-        <v>2123</v>
-      </c>
-      <c r="AM46" s="91" t="s">
-        <v>1775</v>
+        <v>2134</v>
+      </c>
+      <c r="AE46" s="27" t="s">
+        <v>2135</v>
+      </c>
+      <c r="AF46" s="27" t="s">
+        <v>2136</v>
+      </c>
+      <c r="AG46" s="27" t="s">
+        <v>2137</v>
+      </c>
+      <c r="AH46" s="27" t="s">
+        <v>2138</v>
+      </c>
+      <c r="AI46" s="27" t="s">
+        <v>2139</v>
+      </c>
+      <c r="AJ46" s="27" t="s">
+        <v>2140</v>
+      </c>
+      <c r="AK46" s="112" t="s">
+        <v>2141</v>
+      </c>
+      <c r="AL46" s="105" t="s">
+        <v>2142</v>
+      </c>
+      <c r="AM46" s="105" t="s">
+        <v>1791</v>
       </c>
       <c r="AP46" s="9"/>
       <c r="AQ46" s="35"/>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="87"/>
-      <c r="D47" s="1"/>
+      <c r="A47" s="99" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="E47" s="103" t="s">
+        <v>2145</v>
+      </c>
+      <c r="F47" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G47" s="103" t="s">
+        <v>2670</v>
+      </c>
+      <c r="H47" s="27" t="s">
+        <v>490</v>
+      </c>
+      <c r="I47" s="113" t="s">
+        <v>2671</v>
+      </c>
+      <c r="J47" s="27" t="s">
+        <v>2148</v>
+      </c>
+      <c r="K47" s="27" t="s">
+        <v>2149</v>
+      </c>
+      <c r="L47" s="112" t="s">
+        <v>2150</v>
+      </c>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="27"/>
+      <c r="S47" s="27"/>
+      <c r="T47" s="27"/>
+      <c r="U47" s="27"/>
+      <c r="V47" s="27"/>
+      <c r="W47" s="27"/>
+      <c r="X47" s="27"/>
+      <c r="Y47" s="27"/>
+      <c r="Z47" s="27"/>
+      <c r="AA47" s="27"/>
+      <c r="AB47" s="112"/>
+      <c r="AC47" s="27" t="s">
+        <v>2151</v>
+      </c>
+      <c r="AD47" s="89" t="s">
+        <v>2152</v>
+      </c>
+      <c r="AE47" s="27" t="s">
+        <v>2153</v>
+      </c>
+      <c r="AF47" s="27" t="s">
+        <v>2154</v>
+      </c>
+      <c r="AG47" s="27" t="s">
+        <v>2155</v>
+      </c>
+      <c r="AH47" s="101" t="s">
+        <v>2156</v>
+      </c>
+      <c r="AI47" s="101" t="s">
+        <v>2157</v>
+      </c>
+      <c r="AJ47" s="101" t="s">
+        <v>2158</v>
+      </c>
+      <c r="AK47" s="101" t="s">
+        <v>2159</v>
+      </c>
+      <c r="AL47" s="105" t="s">
+        <v>2160</v>
+      </c>
+      <c r="AM47" s="105"/>
       <c r="AP47" s="9"/>
       <c r="AQ47" s="35"/>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="99" t="s">
-        <v>481</v>
+        <v>1687</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" s="27" t="s">
-        <v>482</v>
+        <v>2</v>
       </c>
       <c r="D48" s="1" t="n">
-        <v>118</v>
-      </c>
-      <c r="E48" s="101" t="s">
-        <v>2126</v>
+        <v>8</v>
+      </c>
+      <c r="E48" s="103" t="s">
+        <v>2161</v>
       </c>
       <c r="F48" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G48" s="89" t="s">
-        <v>2127</v>
-      </c>
-      <c r="H48" s="112" t="s">
-        <v>2128</v>
+      <c r="G48" s="103" t="s">
+        <v>2672</v>
+      </c>
+      <c r="H48" s="114" t="n">
+        <v>46175</v>
       </c>
       <c r="I48" s="113" t="s">
-        <v>2669</v>
+        <v>2673</v>
       </c>
       <c r="J48" s="27" t="s">
-        <v>2130</v>
+        <v>2164</v>
       </c>
       <c r="K48" s="27" t="s">
-        <v>2131</v>
+        <v>2165</v>
       </c>
       <c r="L48" s="112" t="s">
-        <v>2132</v>
-      </c>
-      <c r="M48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="N48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="O48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="P48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="R48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="S48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="T48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="U48" s="27" t="s">
-        <v>84</v>
-      </c>
+        <v>2166</v>
+      </c>
+      <c r="M48" s="27"/>
+      <c r="N48" s="27"/>
+      <c r="O48" s="27"/>
+      <c r="P48" s="27"/>
+      <c r="Q48" s="27"/>
+      <c r="R48" s="27"/>
+      <c r="S48" s="27"/>
+      <c r="T48" s="27"/>
+      <c r="U48" s="27"/>
       <c r="V48" s="27"/>
-      <c r="W48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="X48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y48" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z48" s="27" t="s">
-        <v>84</v>
-      </c>
+      <c r="W48" s="27"/>
+      <c r="X48" s="27"/>
+      <c r="Y48" s="27"/>
+      <c r="Z48" s="27"/>
       <c r="AA48" s="27"/>
-      <c r="AB48" s="112" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC48" s="101" t="s">
-        <v>2133</v>
-      </c>
-      <c r="AD48" s="101" t="s">
-        <v>2134</v>
+      <c r="AB48" s="112"/>
+      <c r="AC48" s="27" t="s">
+        <v>2167</v>
+      </c>
+      <c r="AD48" s="89" t="s">
+        <v>2168</v>
       </c>
       <c r="AE48" s="27" t="s">
-        <v>2135</v>
+        <v>2169</v>
       </c>
       <c r="AF48" s="27" t="s">
-        <v>2136</v>
+        <v>2170</v>
       </c>
       <c r="AG48" s="27" t="s">
-        <v>2137</v>
-      </c>
-      <c r="AH48" s="27" t="s">
-        <v>2138</v>
-      </c>
-      <c r="AI48" s="27" t="s">
-        <v>2139</v>
-      </c>
-      <c r="AJ48" s="27" t="s">
-        <v>2140</v>
-      </c>
-      <c r="AK48" s="112" t="s">
-        <v>2141</v>
+        <v>2171</v>
+      </c>
+      <c r="AH48" s="101" t="s">
+        <v>2172</v>
+      </c>
+      <c r="AI48" s="101" t="s">
+        <v>2173</v>
+      </c>
+      <c r="AJ48" s="101" t="s">
+        <v>2174</v>
+      </c>
+      <c r="AK48" s="101" t="s">
+        <v>2175</v>
       </c>
       <c r="AL48" s="105" t="s">
-        <v>2142</v>
-      </c>
-      <c r="AM48" s="105" t="s">
-        <v>1791</v>
-      </c>
+        <v>2176</v>
+      </c>
+      <c r="AM48" s="105"/>
       <c r="AP48" s="9"/>
       <c r="AQ48" s="35"/>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="99" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B49" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D49" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="E49" s="103" t="s">
-        <v>2145</v>
+        <v>2177</v>
       </c>
       <c r="F49" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G49" s="103" t="s">
-        <v>2670</v>
-      </c>
-      <c r="H49" s="27" t="s">
-        <v>490</v>
-      </c>
-      <c r="I49" s="113" t="s">
-        <v>2671</v>
+        <v>2674</v>
+      </c>
+      <c r="H49" s="114" t="n">
+        <v>46266</v>
+      </c>
+      <c r="I49" s="88" t="s">
+        <v>2675</v>
       </c>
       <c r="J49" s="27" t="s">
-        <v>2148</v>
+        <v>2180</v>
       </c>
       <c r="K49" s="27" t="s">
-        <v>2149</v>
+        <v>2181</v>
       </c>
       <c r="L49" s="112" t="s">
-        <v>2150</v>
+        <v>2182</v>
       </c>
       <c r="M49" s="27"/>
       <c r="N49" s="27"/>
@@ -40013,73 +39899,48 @@
       <c r="AA49" s="27"/>
       <c r="AB49" s="112"/>
       <c r="AC49" s="27" t="s">
-        <v>2151</v>
+        <v>2183</v>
       </c>
       <c r="AD49" s="89" t="s">
-        <v>2152</v>
+        <v>2184</v>
       </c>
       <c r="AE49" s="27" t="s">
-        <v>2153</v>
+        <v>2185</v>
       </c>
       <c r="AF49" s="27" t="s">
-        <v>2154</v>
+        <v>2186</v>
       </c>
       <c r="AG49" s="27" t="s">
-        <v>2155</v>
+        <v>2187</v>
       </c>
       <c r="AH49" s="101" t="s">
-        <v>2156</v>
+        <v>2188</v>
       </c>
       <c r="AI49" s="101" t="s">
-        <v>2157</v>
+        <v>2189</v>
       </c>
       <c r="AJ49" s="101" t="s">
-        <v>2158</v>
+        <v>2190</v>
       </c>
       <c r="AK49" s="101" t="s">
-        <v>2159</v>
+        <v>2191</v>
       </c>
       <c r="AL49" s="105" t="s">
-        <v>2160</v>
+        <v>87</v>
       </c>
       <c r="AM49" s="105"/>
       <c r="AP49" s="9"/>
       <c r="AQ49" s="35"/>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="99" t="s">
-        <v>1687</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="E50" s="103" t="s">
-        <v>2161</v>
-      </c>
-      <c r="F50" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G50" s="103" t="s">
-        <v>2672</v>
-      </c>
-      <c r="H50" s="114" t="n">
-        <v>46175</v>
-      </c>
-      <c r="I50" s="113" t="s">
-        <v>2673</v>
-      </c>
-      <c r="J50" s="27" t="s">
-        <v>2164</v>
-      </c>
-      <c r="K50" s="27" t="s">
-        <v>2165</v>
-      </c>
-      <c r="L50" s="112" t="s">
-        <v>2166</v>
-      </c>
+      <c r="A50" s="87"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="103"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="113"/>
+      <c r="J50" s="27"/>
+      <c r="K50" s="27"/>
+      <c r="L50" s="112"/>
       <c r="M50" s="27"/>
       <c r="N50" s="27"/>
       <c r="O50" s="27"/>
@@ -40096,504 +39957,670 @@
       <c r="Z50" s="27"/>
       <c r="AA50" s="27"/>
       <c r="AB50" s="112"/>
-      <c r="AC50" s="27" t="s">
-        <v>2167</v>
-      </c>
-      <c r="AD50" s="89" t="s">
-        <v>2168</v>
-      </c>
-      <c r="AE50" s="27" t="s">
-        <v>2169</v>
-      </c>
-      <c r="AF50" s="27" t="s">
-        <v>2170</v>
-      </c>
-      <c r="AG50" s="27" t="s">
-        <v>2171</v>
-      </c>
-      <c r="AH50" s="101" t="s">
-        <v>2172</v>
-      </c>
-      <c r="AI50" s="101" t="s">
-        <v>2173</v>
-      </c>
-      <c r="AJ50" s="101" t="s">
-        <v>2174</v>
-      </c>
-      <c r="AK50" s="101" t="s">
-        <v>2175</v>
-      </c>
-      <c r="AL50" s="105" t="s">
-        <v>2176</v>
-      </c>
+      <c r="AC50" s="27"/>
+      <c r="AE50" s="27"/>
+      <c r="AF50" s="27"/>
+      <c r="AG50" s="27"/>
+      <c r="AH50" s="27"/>
+      <c r="AI50" s="27"/>
+      <c r="AJ50" s="27"/>
+      <c r="AK50" s="112"/>
+      <c r="AL50" s="105"/>
       <c r="AM50" s="105"/>
       <c r="AP50" s="9"/>
       <c r="AQ50" s="35"/>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="99" t="s">
-        <v>1688</v>
+        <v>2192</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C51" s="27" t="s">
+        <v>401</v>
       </c>
       <c r="D51" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="E51" s="103" t="s">
-        <v>2177</v>
+        <v>2237</v>
+      </c>
+      <c r="E51" s="27" t="n">
+        <v>2237</v>
       </c>
       <c r="F51" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="G51" s="103" t="s">
-        <v>2674</v>
-      </c>
-      <c r="H51" s="114" t="n">
-        <v>46266</v>
-      </c>
-      <c r="I51" s="88" t="s">
-        <v>2675</v>
-      </c>
-      <c r="J51" s="27" t="s">
-        <v>2180</v>
-      </c>
-      <c r="K51" s="27" t="s">
-        <v>2181</v>
-      </c>
-      <c r="L51" s="112" t="s">
-        <v>2182</v>
-      </c>
-      <c r="M51" s="27"/>
-      <c r="N51" s="27"/>
-      <c r="O51" s="27"/>
-      <c r="P51" s="27"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="27"/>
-      <c r="S51" s="27"/>
-      <c r="T51" s="27"/>
-      <c r="U51" s="27"/>
+      <c r="G51" s="89" t="s">
+        <v>2193</v>
+      </c>
+      <c r="H51" s="89" t="s">
+        <v>525</v>
+      </c>
+      <c r="I51" s="90" t="s">
+        <v>2194</v>
+      </c>
+      <c r="J51" s="89" t="s">
+        <v>2195</v>
+      </c>
+      <c r="K51" s="89" t="s">
+        <v>2196</v>
+      </c>
+      <c r="L51" s="90" t="s">
+        <v>2197</v>
+      </c>
+      <c r="M51" s="89" t="s">
+        <v>2198</v>
+      </c>
+      <c r="N51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="O51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="P51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="R51" s="73" t="s">
+        <v>2676</v>
+      </c>
+      <c r="S51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="T51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="U51" s="27" t="s">
+        <v>84</v>
+      </c>
       <c r="V51" s="27"/>
-      <c r="W51" s="27"/>
-      <c r="X51" s="27"/>
-      <c r="Y51" s="27"/>
-      <c r="Z51" s="27"/>
+      <c r="W51" s="89" t="s">
+        <v>2200</v>
+      </c>
+      <c r="X51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y51" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z51" s="27" t="s">
+        <v>84</v>
+      </c>
       <c r="AA51" s="27"/>
-      <c r="AB51" s="112"/>
-      <c r="AC51" s="27" t="s">
-        <v>2183</v>
+      <c r="AB51" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC51" s="89" t="s">
+        <v>2201</v>
       </c>
       <c r="AD51" s="89" t="s">
-        <v>2184</v>
-      </c>
-      <c r="AE51" s="27" t="s">
-        <v>2185</v>
-      </c>
-      <c r="AF51" s="27" t="s">
-        <v>2186</v>
-      </c>
-      <c r="AG51" s="27" t="s">
-        <v>2187</v>
-      </c>
-      <c r="AH51" s="101" t="s">
-        <v>2188</v>
-      </c>
-      <c r="AI51" s="101" t="s">
-        <v>2189</v>
-      </c>
-      <c r="AJ51" s="101" t="s">
-        <v>2190</v>
-      </c>
-      <c r="AK51" s="101" t="s">
-        <v>2191</v>
-      </c>
-      <c r="AL51" s="105" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM51" s="105"/>
-      <c r="AP51" s="9"/>
-      <c r="AQ51" s="35"/>
+        <v>2202</v>
+      </c>
+      <c r="AE51" s="89" t="s">
+        <v>2203</v>
+      </c>
+      <c r="AF51" s="89" t="s">
+        <v>2204</v>
+      </c>
+      <c r="AG51" s="89" t="s">
+        <v>2205</v>
+      </c>
+      <c r="AH51" s="89" t="s">
+        <v>2206</v>
+      </c>
+      <c r="AI51" s="89" t="s">
+        <v>2207</v>
+      </c>
+      <c r="AJ51" s="89" t="s">
+        <v>2208</v>
+      </c>
+      <c r="AK51" s="90" t="s">
+        <v>2209</v>
+      </c>
+      <c r="AL51" s="91" t="s">
+        <v>2210</v>
+      </c>
+      <c r="AM51" s="91" t="s">
+        <v>1775</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="87"/>
       <c r="D52" s="1"/>
-      <c r="E52" s="103"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="113"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="112"/>
-      <c r="M52" s="27"/>
       <c r="N52" s="27"/>
       <c r="O52" s="27"/>
       <c r="P52" s="27"/>
       <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
+      <c r="R52" s="73"/>
       <c r="S52" s="27"/>
       <c r="T52" s="27"/>
       <c r="U52" s="27"/>
       <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
       <c r="X52" s="27"/>
       <c r="Y52" s="27"/>
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
       <c r="AB52" s="112"/>
-      <c r="AC52" s="27"/>
-      <c r="AE52" s="27"/>
-      <c r="AF52" s="27"/>
-      <c r="AG52" s="27"/>
-      <c r="AH52" s="27"/>
-      <c r="AI52" s="27"/>
-      <c r="AJ52" s="27"/>
-      <c r="AK52" s="112"/>
-      <c r="AL52" s="105"/>
-      <c r="AM52" s="105"/>
-      <c r="AP52" s="9"/>
-      <c r="AQ52" s="35"/>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="99" t="s">
-        <v>2192</v>
+        <v>2214</v>
       </c>
       <c r="B53" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C53" s="27" t="s">
-        <v>401</v>
+      <c r="C53" s="27" t="n">
+        <v>1999</v>
       </c>
       <c r="D53" s="1" t="n">
-        <v>2237</v>
+        <v>16</v>
       </c>
       <c r="E53" s="27" t="n">
-        <v>2237</v>
+        <v>19</v>
       </c>
       <c r="F53" s="27" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="G53" s="89" t="s">
-        <v>2193</v>
+        <v>2215</v>
       </c>
       <c r="H53" s="89" t="s">
-        <v>525</v>
+        <v>2677</v>
       </c>
       <c r="I53" s="90" t="s">
-        <v>2194</v>
+        <v>84</v>
       </c>
       <c r="J53" s="89" t="s">
-        <v>2195</v>
+        <v>2218</v>
       </c>
       <c r="K53" s="89" t="s">
-        <v>2196</v>
+        <v>84</v>
       </c>
       <c r="L53" s="90" t="s">
-        <v>2197</v>
+        <v>84</v>
       </c>
       <c r="M53" s="89" t="s">
-        <v>2198</v>
-      </c>
-      <c r="N53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="O53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="P53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="R53" s="73" t="s">
-        <v>2676</v>
-      </c>
-      <c r="S53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="T53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="U53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="V53" s="27"/>
+        <v>84</v>
+      </c>
+      <c r="N53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U53" s="89" t="s">
+        <v>84</v>
+      </c>
       <c r="W53" s="89" t="s">
-        <v>2200</v>
-      </c>
-      <c r="X53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z53" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA53" s="27"/>
-      <c r="AB53" s="112" t="s">
+        <v>84</v>
+      </c>
+      <c r="X53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z53" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB53" s="90" t="s">
         <v>84</v>
       </c>
       <c r="AC53" s="89" t="s">
-        <v>2201</v>
-      </c>
-      <c r="AD53" s="89" t="s">
-        <v>2202</v>
-      </c>
-      <c r="AE53" s="89" t="s">
-        <v>2203</v>
-      </c>
-      <c r="AF53" s="89" t="s">
-        <v>2204</v>
-      </c>
-      <c r="AG53" s="89" t="s">
-        <v>2205</v>
-      </c>
-      <c r="AH53" s="89" t="s">
-        <v>2206</v>
-      </c>
-      <c r="AI53" s="89" t="s">
-        <v>2207</v>
-      </c>
-      <c r="AJ53" s="89" t="s">
-        <v>2208</v>
-      </c>
-      <c r="AK53" s="90" t="s">
-        <v>2209</v>
+        <v>2219</v>
+      </c>
+      <c r="AD53" s="101" t="s">
+        <v>2220</v>
+      </c>
+      <c r="AE53" s="101" t="s">
+        <v>2221</v>
+      </c>
+      <c r="AF53" s="101" t="s">
+        <v>2222</v>
+      </c>
+      <c r="AG53" s="101" t="s">
+        <v>2223</v>
+      </c>
+      <c r="AH53" s="101" t="s">
+        <v>2224</v>
+      </c>
+      <c r="AI53" s="101" t="s">
+        <v>2225</v>
+      </c>
+      <c r="AJ53" s="101" t="s">
+        <v>2226</v>
+      </c>
+      <c r="AK53" s="102" t="s">
+        <v>2227</v>
       </c>
       <c r="AL53" s="91" t="s">
-        <v>2210</v>
+        <v>2228</v>
       </c>
       <c r="AM53" s="91" t="s">
         <v>1775</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="87"/>
-      <c r="D54" s="1"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-      <c r="Q54" s="27"/>
-      <c r="R54" s="73"/>
-      <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-      <c r="U54" s="27"/>
-      <c r="V54" s="27"/>
-      <c r="X54" s="27"/>
-      <c r="Y54" s="27"/>
-      <c r="Z54" s="27"/>
-      <c r="AA54" s="27"/>
-      <c r="AB54" s="112"/>
-    </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="87" t="s">
-        <v>2213</v>
+        <v>2232</v>
       </c>
       <c r="B55" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D55" s="1"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="73"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
-      <c r="AA55" s="27"/>
-      <c r="AB55" s="112"/>
+      <c r="C55" s="27" t="s">
+        <v>571</v>
+      </c>
+      <c r="E55" s="100" t="n">
+        <v>1438</v>
+      </c>
+      <c r="F55" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="L55" s="89"/>
+      <c r="M55" s="1"/>
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="AC55" s="89" t="s">
+        <v>2234</v>
+      </c>
+      <c r="AD55" s="89" t="s">
+        <v>2235</v>
+      </c>
+      <c r="AE55" s="89" t="s">
+        <v>2236</v>
+      </c>
+      <c r="AF55" s="89" t="s">
+        <v>2237</v>
+      </c>
+      <c r="AG55" s="89" t="s">
+        <v>2238</v>
+      </c>
+      <c r="AH55" s="89" t="s">
+        <v>2239</v>
+      </c>
+      <c r="AI55" s="89" t="s">
+        <v>2240</v>
+      </c>
+      <c r="AJ55" s="89" t="s">
+        <v>2241</v>
+      </c>
+      <c r="AK55" s="90" t="s">
+        <v>2242</v>
+      </c>
+      <c r="AM55" s="91" t="s">
+        <v>1775</v>
+      </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="87"/>
-      <c r="D56" s="1"/>
-      <c r="N56" s="27"/>
-      <c r="O56" s="27"/>
-      <c r="P56" s="27"/>
-      <c r="Q56" s="27"/>
-      <c r="R56" s="73"/>
-      <c r="S56" s="27"/>
-      <c r="T56" s="27"/>
-      <c r="U56" s="27"/>
-      <c r="V56" s="27"/>
-      <c r="X56" s="27"/>
-      <c r="Y56" s="27"/>
-      <c r="Z56" s="27"/>
-      <c r="AA56" s="27"/>
-      <c r="AB56" s="112"/>
+      <c r="A56" s="1" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C56" s="27" t="n">
+        <v>2012</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="E56" s="27" t="n">
+        <v>139</v>
+      </c>
+      <c r="F56" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G56" s="89" t="s">
+        <v>2246</v>
+      </c>
+      <c r="H56" s="89" t="s">
+        <v>2247</v>
+      </c>
+      <c r="I56" s="90" t="s">
+        <v>2248</v>
+      </c>
+      <c r="L56" s="89"/>
+      <c r="M56" s="1"/>
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="AC56" s="89" t="s">
+        <v>2249</v>
+      </c>
+      <c r="AD56" s="89" t="s">
+        <v>2250</v>
+      </c>
+      <c r="AE56" s="89" t="s">
+        <v>2251</v>
+      </c>
+      <c r="AF56" s="89" t="s">
+        <v>2252</v>
+      </c>
+      <c r="AG56" s="89" t="s">
+        <v>2253</v>
+      </c>
+      <c r="AH56" s="89" t="s">
+        <v>2254</v>
+      </c>
+      <c r="AI56" s="89" t="s">
+        <v>2255</v>
+      </c>
+      <c r="AJ56" s="89" t="s">
+        <v>2256</v>
+      </c>
+      <c r="AK56" s="90" t="s">
+        <v>2257</v>
+      </c>
+      <c r="AL56" s="1" t="s">
+        <v>2258</v>
+      </c>
+      <c r="AM56" s="91" t="s">
+        <v>1775</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="99" t="s">
-        <v>2214</v>
+      <c r="A57" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" s="27" t="n">
-        <v>1999</v>
+        <v>2</v>
       </c>
       <c r="D57" s="1" t="n">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="E57" s="27" t="n">
-        <v>19</v>
+        <v>83</v>
       </c>
       <c r="F57" s="27" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G57" s="89" t="s">
-        <v>2215</v>
+        <v>2261</v>
       </c>
       <c r="H57" s="89" t="s">
-        <v>2677</v>
+        <v>582</v>
       </c>
       <c r="I57" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="J57" s="89" t="s">
-        <v>2218</v>
-      </c>
-      <c r="K57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L57" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="M57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="N57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="S57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z57" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB57" s="90" t="s">
-        <v>84</v>
-      </c>
+        <v>2261</v>
+      </c>
+      <c r="L57" s="89"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
       <c r="AC57" s="89" t="s">
-        <v>2219</v>
-      </c>
-      <c r="AD57" s="101" t="s">
-        <v>2220</v>
-      </c>
-      <c r="AE57" s="101" t="s">
-        <v>2221</v>
-      </c>
-      <c r="AF57" s="101" t="s">
-        <v>2222</v>
-      </c>
-      <c r="AG57" s="101" t="s">
-        <v>2223</v>
-      </c>
-      <c r="AH57" s="101" t="s">
-        <v>2224</v>
-      </c>
-      <c r="AI57" s="101" t="s">
-        <v>2225</v>
-      </c>
-      <c r="AJ57" s="101" t="s">
-        <v>2226</v>
-      </c>
-      <c r="AK57" s="102" t="s">
-        <v>2227</v>
+        <v>2262</v>
+      </c>
+      <c r="AD57" s="89" t="s">
+        <v>2263</v>
+      </c>
+      <c r="AE57" s="89" t="s">
+        <v>2264</v>
+      </c>
+      <c r="AF57" s="89" t="s">
+        <v>2265</v>
+      </c>
+      <c r="AG57" s="89" t="s">
+        <v>2266</v>
+      </c>
+      <c r="AH57" s="89" t="s">
+        <v>2267</v>
+      </c>
+      <c r="AI57" s="89" t="s">
+        <v>2268</v>
+      </c>
+      <c r="AJ57" s="89" t="s">
+        <v>2269</v>
+      </c>
+      <c r="AK57" s="90" t="s">
+        <v>2270</v>
       </c>
       <c r="AL57" s="91" t="s">
-        <v>2228</v>
+        <v>2271</v>
       </c>
       <c r="AM57" s="91" t="s">
         <v>1775</v>
       </c>
     </row>
+    <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="27" t="n">
+        <v>68</v>
+      </c>
+      <c r="F58" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G58" s="89" t="s">
+        <v>2274</v>
+      </c>
+      <c r="H58" s="89" t="s">
+        <v>2275</v>
+      </c>
+      <c r="I58" s="90" t="s">
+        <v>2274</v>
+      </c>
+      <c r="L58" s="89"/>
+      <c r="M58" s="1"/>
+      <c r="N58" s="1"/>
+      <c r="O58" s="1"/>
+      <c r="P58" s="1"/>
+      <c r="AC58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ58" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK58" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM58" s="91" t="s">
+        <v>1775</v>
+      </c>
+    </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>2231</v>
+        <v>2276</v>
       </c>
       <c r="B59" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="E59" s="27" t="n">
+        <v>148</v>
+      </c>
+      <c r="F59" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G59" s="89" t="s">
+        <v>2277</v>
+      </c>
+      <c r="H59" s="89" t="s">
+        <v>2278</v>
+      </c>
+      <c r="I59" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="L59" s="89"/>
+      <c r="M59" s="1"/>
+      <c r="N59" s="1"/>
+      <c r="O59" s="1"/>
+      <c r="P59" s="1"/>
+      <c r="AC59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ59" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK59" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM59" s="91" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="27" t="n">
+        <v>70</v>
+      </c>
+      <c r="F60" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G60" s="89" t="s">
+        <v>2280</v>
+      </c>
+      <c r="H60" s="89" t="s">
+        <v>2281</v>
+      </c>
+      <c r="I60" s="90" t="s">
+        <v>2280</v>
+      </c>
+      <c r="L60" s="89"/>
+      <c r="M60" s="1"/>
+      <c r="N60" s="1"/>
+      <c r="O60" s="1"/>
+      <c r="P60" s="1"/>
+      <c r="AC60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ60" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK60" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM60" s="91" t="s">
+        <v>1775</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="87" t="s">
-        <v>2232</v>
+      <c r="A61" s="1" t="s">
+        <v>2282</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>571</v>
-      </c>
-      <c r="E61" s="100" t="n">
-        <v>1438</v>
+        <v>2</v>
+      </c>
+      <c r="E61" s="27" t="n">
+        <v>158</v>
       </c>
       <c r="F61" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="L61" s="89"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
+      <c r="G61" s="89" t="s">
+        <v>2283</v>
+      </c>
+      <c r="H61" s="89" t="s">
+        <v>2284</v>
+      </c>
+      <c r="I61" s="90" t="s">
+        <v>2283</v>
+      </c>
       <c r="AC61" s="89" t="s">
-        <v>2234</v>
+        <v>84</v>
       </c>
       <c r="AD61" s="89" t="s">
-        <v>2235</v>
+        <v>84</v>
       </c>
       <c r="AE61" s="89" t="s">
-        <v>2236</v>
+        <v>84</v>
       </c>
       <c r="AF61" s="89" t="s">
-        <v>2237</v>
+        <v>84</v>
       </c>
       <c r="AG61" s="89" t="s">
-        <v>2238</v>
+        <v>84</v>
       </c>
       <c r="AH61" s="89" t="s">
-        <v>2239</v>
+        <v>84</v>
       </c>
       <c r="AI61" s="89" t="s">
-        <v>2240</v>
+        <v>84</v>
       </c>
       <c r="AJ61" s="89" t="s">
-        <v>2241</v>
+        <v>84</v>
       </c>
       <c r="AK61" s="90" t="s">
-        <v>2242</v>
+        <v>84</v>
       </c>
       <c r="AM61" s="91" t="s">
         <v>1775</v>
@@ -40601,462 +40628,593 @@
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>2244</v>
+        <v>575</v>
       </c>
       <c r="B62" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C62" s="27" t="n">
-        <v>2012</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>199</v>
-      </c>
       <c r="E62" s="27" t="n">
-        <v>139</v>
+        <v>772</v>
       </c>
       <c r="F62" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G62" s="89" t="s">
-        <v>2246</v>
+        <v>2286</v>
       </c>
       <c r="H62" s="89" t="s">
-        <v>2247</v>
+        <v>581</v>
       </c>
       <c r="I62" s="90" t="s">
-        <v>2248</v>
-      </c>
-      <c r="L62" s="89"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
+        <v>2286</v>
+      </c>
       <c r="AC62" s="89" t="s">
-        <v>2249</v>
+        <v>2287</v>
       </c>
       <c r="AD62" s="89" t="s">
-        <v>2250</v>
+        <v>2288</v>
       </c>
       <c r="AE62" s="89" t="s">
-        <v>2251</v>
+        <v>2289</v>
       </c>
       <c r="AF62" s="89" t="s">
-        <v>2252</v>
+        <v>2290</v>
       </c>
       <c r="AG62" s="89" t="s">
-        <v>2253</v>
+        <v>2291</v>
       </c>
       <c r="AH62" s="89" t="s">
-        <v>2254</v>
+        <v>2292</v>
       </c>
       <c r="AI62" s="89" t="s">
-        <v>2255</v>
+        <v>2293</v>
       </c>
       <c r="AJ62" s="89" t="s">
-        <v>2256</v>
+        <v>2294</v>
       </c>
       <c r="AK62" s="90" t="s">
-        <v>2257</v>
-      </c>
-      <c r="AL62" s="1" t="s">
-        <v>2258</v>
+        <v>2295</v>
       </c>
       <c r="AM62" s="91" t="s">
         <v>1775</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="E63" s="27" t="n">
-        <v>83</v>
-      </c>
-      <c r="F63" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G63" s="89" t="s">
-        <v>2261</v>
-      </c>
-      <c r="H63" s="89" t="s">
-        <v>582</v>
-      </c>
-      <c r="I63" s="90" t="s">
-        <v>2261</v>
-      </c>
-      <c r="L63" s="89"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="AC63" s="89" t="s">
-        <v>2262</v>
-      </c>
-      <c r="AD63" s="89" t="s">
-        <v>2263</v>
-      </c>
-      <c r="AE63" s="89" t="s">
-        <v>2264</v>
-      </c>
-      <c r="AF63" s="89" t="s">
-        <v>2265</v>
-      </c>
-      <c r="AG63" s="89" t="s">
-        <v>2266</v>
-      </c>
-      <c r="AH63" s="89" t="s">
-        <v>2267</v>
-      </c>
-      <c r="AI63" s="89" t="s">
-        <v>2268</v>
-      </c>
-      <c r="AJ63" s="89" t="s">
-        <v>2269</v>
-      </c>
-      <c r="AK63" s="90" t="s">
-        <v>2270</v>
-      </c>
-      <c r="AL63" s="91" t="s">
-        <v>2271</v>
-      </c>
-      <c r="AM63" s="91" t="s">
-        <v>1775</v>
-      </c>
-    </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
-        <v>2273</v>
+      <c r="A64" s="107" t="s">
+        <v>2297</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="C64" s="27" t="s">
+        <v>605</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>2909</v>
       </c>
       <c r="E64" s="27" t="n">
-        <v>68</v>
+        <v>3930</v>
       </c>
       <c r="F64" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G64" s="89" t="s">
-        <v>2274</v>
+        <v>2298</v>
       </c>
       <c r="H64" s="89" t="s">
-        <v>2275</v>
+        <v>610</v>
       </c>
       <c r="I64" s="90" t="s">
-        <v>2274</v>
-      </c>
-      <c r="L64" s="89"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
+        <v>2299</v>
+      </c>
+      <c r="J64" s="89" t="s">
+        <v>2300</v>
+      </c>
+      <c r="K64" s="89" t="s">
+        <v>2301</v>
+      </c>
+      <c r="L64" s="90" t="s">
+        <v>2302</v>
+      </c>
+      <c r="M64" s="89" t="s">
+        <v>2303</v>
+      </c>
+      <c r="N64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T64" s="89" t="s">
+        <v>2304</v>
+      </c>
+      <c r="U64" s="89" t="s">
+        <v>2305</v>
+      </c>
+      <c r="V64" s="89" t="s">
+        <v>2306</v>
+      </c>
+      <c r="W64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z64" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB64" s="90" t="s">
+        <v>84</v>
+      </c>
       <c r="AC64" s="89" t="s">
         <v>84</v>
       </c>
       <c r="AD64" s="89" t="s">
-        <v>84</v>
+        <v>2307</v>
       </c>
       <c r="AE64" s="89" t="s">
-        <v>84</v>
+        <v>2308</v>
       </c>
       <c r="AF64" s="89" t="s">
         <v>84</v>
       </c>
       <c r="AG64" s="89" t="s">
-        <v>84</v>
+        <v>2309</v>
       </c>
       <c r="AH64" s="89" t="s">
-        <v>84</v>
+        <v>2310</v>
       </c>
       <c r="AI64" s="89" t="s">
-        <v>84</v>
+        <v>2311</v>
       </c>
       <c r="AJ64" s="89" t="s">
-        <v>84</v>
+        <v>2312</v>
       </c>
       <c r="AK64" s="90" t="s">
-        <v>84</v>
+        <v>2313</v>
+      </c>
+      <c r="AL64" s="4" t="s">
+        <v>2314</v>
       </c>
       <c r="AM64" s="91" t="s">
         <v>1775</v>
       </c>
+      <c r="AP64" s="9"/>
+      <c r="AQ64" s="2"/>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
-        <v>2276</v>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="27" t="n">
-        <v>148</v>
-      </c>
-      <c r="F65" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G65" s="89" t="s">
-        <v>2277</v>
-      </c>
-      <c r="H65" s="89" t="s">
-        <v>2278</v>
-      </c>
-      <c r="I65" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="L65" s="89"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="AC65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ65" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK65" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM65" s="91" t="s">
-        <v>1775</v>
-      </c>
+      <c r="A65" s="87"/>
+      <c r="D65" s="1"/>
+      <c r="AL65" s="4"/>
+      <c r="AP65" s="9"/>
+      <c r="AQ65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
-        <v>2279</v>
+      <c r="A66" s="99" t="s">
+        <v>2317</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E66" s="27" t="n">
-        <v>70</v>
+        <v>1</v>
+      </c>
+      <c r="C66" s="27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>106</v>
+      </c>
+      <c r="E66" s="100" t="n">
+        <v>106</v>
       </c>
       <c r="F66" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G66" s="89" t="s">
-        <v>2280</v>
+        <v>2318</v>
       </c>
       <c r="H66" s="89" t="s">
-        <v>2281</v>
+        <v>651</v>
       </c>
       <c r="I66" s="90" t="s">
-        <v>2280</v>
-      </c>
-      <c r="L66" s="89"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
+        <v>2319</v>
+      </c>
+      <c r="J66" s="89" t="s">
+        <v>2320</v>
+      </c>
+      <c r="K66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L66" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="M66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z66" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB66" s="90" t="s">
+        <v>84</v>
+      </c>
       <c r="AC66" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD66" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE66" s="89" t="s">
-        <v>84</v>
+        <v>2321</v>
+      </c>
+      <c r="AD66" s="101" t="s">
+        <v>2322</v>
+      </c>
+      <c r="AE66" s="101" t="s">
+        <v>2323</v>
       </c>
       <c r="AF66" s="89" t="s">
-        <v>84</v>
+        <v>2324</v>
       </c>
       <c r="AG66" s="89" t="s">
-        <v>84</v>
+        <v>2325</v>
       </c>
       <c r="AH66" s="89" t="s">
-        <v>84</v>
+        <v>2326</v>
       </c>
       <c r="AI66" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ66" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK66" s="90" t="s">
-        <v>84</v>
+        <v>2327</v>
+      </c>
+      <c r="AJ66" s="101" t="s">
+        <v>2328</v>
+      </c>
+      <c r="AK66" s="102" t="s">
+        <v>2329</v>
+      </c>
+      <c r="AL66" s="4" t="s">
+        <v>2330</v>
       </c>
       <c r="AM66" s="91" t="s">
         <v>1775</v>
       </c>
+      <c r="AO66" s="57"/>
+      <c r="AP66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
-        <v>2282</v>
-      </c>
-      <c r="B67" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E67" s="27" t="n">
-        <v>158</v>
-      </c>
-      <c r="F67" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="G67" s="89" t="s">
-        <v>2283</v>
-      </c>
-      <c r="H67" s="89" t="s">
-        <v>2284</v>
-      </c>
-      <c r="I67" s="90" t="s">
-        <v>2283</v>
-      </c>
-      <c r="AC67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ67" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK67" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM67" s="91" t="s">
-        <v>1775</v>
-      </c>
+      <c r="A67" s="87"/>
+      <c r="D67" s="1"/>
+      <c r="AD67" s="103"/>
+      <c r="AE67" s="103"/>
+      <c r="AJ67" s="103"/>
+      <c r="AK67" s="104"/>
+      <c r="AL67" s="4"/>
+      <c r="AO67" s="57"/>
+      <c r="AP67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
-        <v>575</v>
+      <c r="A68" s="99" t="s">
+        <v>1679</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E68" s="27" t="n">
-        <v>772</v>
+        <v>1</v>
+      </c>
+      <c r="C68" s="27" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="E68" s="100" t="n">
+        <v>76</v>
       </c>
       <c r="F68" s="27" t="s">
-        <v>67</v>
+        <v>2678</v>
       </c>
       <c r="G68" s="89" t="s">
-        <v>2286</v>
+        <v>663</v>
       </c>
       <c r="H68" s="89" t="s">
-        <v>581</v>
+        <v>664</v>
       </c>
       <c r="I68" s="90" t="s">
-        <v>2286</v>
+        <v>84</v>
+      </c>
+      <c r="J68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="K68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L68" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="M68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z68" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB68" s="90" t="s">
+        <v>84</v>
       </c>
       <c r="AC68" s="89" t="s">
-        <v>2287</v>
+        <v>2334</v>
       </c>
       <c r="AD68" s="89" t="s">
-        <v>2288</v>
+        <v>2335</v>
       </c>
       <c r="AE68" s="89" t="s">
-        <v>2289</v>
+        <v>2336</v>
       </c>
       <c r="AF68" s="89" t="s">
-        <v>2290</v>
+        <v>2337</v>
       </c>
       <c r="AG68" s="89" t="s">
-        <v>2291</v>
+        <v>2338</v>
       </c>
       <c r="AH68" s="89" t="s">
-        <v>2292</v>
+        <v>84</v>
       </c>
       <c r="AI68" s="89" t="s">
-        <v>2293</v>
+        <v>84</v>
       </c>
       <c r="AJ68" s="89" t="s">
-        <v>2294</v>
+        <v>84</v>
       </c>
       <c r="AK68" s="90" t="s">
-        <v>2295</v>
+        <v>84</v>
+      </c>
+      <c r="AL68" s="91" t="s">
+        <v>2339</v>
       </c>
       <c r="AM68" s="91" t="s">
-        <v>1775</v>
-      </c>
+        <v>1791</v>
+      </c>
+      <c r="AO68" s="57"/>
+      <c r="AP68" s="2"/>
+    </row>
+    <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="87"/>
+      <c r="D69" s="1"/>
+      <c r="AO69" s="57"/>
+      <c r="AP69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="87" t="s">
-        <v>2296</v>
+      <c r="A70" s="107" t="s">
+        <v>1680</v>
       </c>
       <c r="B70" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="C70" s="27" t="s">
+        <v>674</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>3672</v>
+      </c>
+      <c r="E70" s="100" t="n">
+        <v>3982</v>
+      </c>
+      <c r="F70" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="G70" s="89" t="s">
+        <v>2342</v>
+      </c>
+      <c r="H70" s="115" t="s">
+        <v>2343</v>
+      </c>
+      <c r="I70" s="90" t="s">
+        <v>2344</v>
+      </c>
+      <c r="J70" s="116"/>
+      <c r="K70" s="116"/>
+      <c r="L70" s="117"/>
+      <c r="M70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB70" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD70" s="89" t="s">
+        <v>2346</v>
+      </c>
+      <c r="AE70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ70" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK70" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AL70" s="91" t="s">
+        <v>2347</v>
+      </c>
+      <c r="AM70" s="91" t="s">
+        <v>1775</v>
+      </c>
+      <c r="AO70" s="9"/>
+      <c r="AP70" s="2"/>
+    </row>
+    <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="87"/>
+      <c r="D71" s="1"/>
+      <c r="J71" s="103"/>
+      <c r="K71" s="103"/>
+      <c r="L71" s="104"/>
+      <c r="AO71" s="9"/>
+      <c r="AP71" s="2"/>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="107" t="s">
-        <v>2297</v>
+      <c r="A72" s="99" t="s">
+        <v>1681</v>
       </c>
       <c r="B72" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C72" s="27" t="s">
-        <v>605</v>
+      <c r="C72" s="27" t="n">
+        <v>2018</v>
       </c>
       <c r="D72" s="1" t="n">
-        <v>2909</v>
-      </c>
-      <c r="E72" s="27" t="n">
-        <v>3930</v>
+        <v>1983</v>
+      </c>
+      <c r="E72" s="100" t="n">
+        <v>1983</v>
       </c>
       <c r="F72" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G72" s="89" t="s">
-        <v>2298</v>
+        <v>2351</v>
       </c>
       <c r="H72" s="89" t="s">
-        <v>610</v>
+        <v>688</v>
       </c>
       <c r="I72" s="90" t="s">
-        <v>2299</v>
+        <v>2352</v>
       </c>
       <c r="J72" s="89" t="s">
-        <v>2300</v>
-      </c>
-      <c r="K72" s="89" t="s">
-        <v>2301</v>
-      </c>
+        <v>2353</v>
+      </c>
+      <c r="K72" s="118"/>
       <c r="L72" s="90" t="s">
-        <v>2302</v>
+        <v>84</v>
       </c>
       <c r="M72" s="89" t="s">
-        <v>2303</v>
+        <v>2355</v>
       </c>
       <c r="N72" s="89" t="s">
         <v>84</v>
@@ -41077,13 +41235,13 @@
         <v>84</v>
       </c>
       <c r="T72" s="89" t="s">
-        <v>2304</v>
+        <v>84</v>
       </c>
       <c r="U72" s="89" t="s">
-        <v>2305</v>
+        <v>84</v>
       </c>
       <c r="V72" s="89" t="s">
-        <v>2306</v>
+        <v>84</v>
       </c>
       <c r="W72" s="89" t="s">
         <v>84</v>
@@ -41100,85 +41258,83 @@
       <c r="AB72" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC72" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD72" s="89" t="s">
-        <v>2307</v>
+      <c r="AC72" s="101" t="s">
+        <v>2356</v>
+      </c>
+      <c r="AD72" s="101" t="s">
+        <v>2357</v>
       </c>
       <c r="AE72" s="89" t="s">
-        <v>2308</v>
+        <v>2358</v>
       </c>
       <c r="AF72" s="89" t="s">
-        <v>84</v>
+        <v>2359</v>
       </c>
       <c r="AG72" s="89" t="s">
-        <v>2309</v>
-      </c>
-      <c r="AH72" s="89" t="s">
-        <v>2310</v>
-      </c>
-      <c r="AI72" s="89" t="s">
-        <v>2311</v>
-      </c>
-      <c r="AJ72" s="89" t="s">
-        <v>2312</v>
-      </c>
-      <c r="AK72" s="90" t="s">
-        <v>2313</v>
-      </c>
-      <c r="AL72" s="4" t="s">
-        <v>2314</v>
+        <v>2360</v>
+      </c>
+      <c r="AH72" s="101" t="s">
+        <v>2361</v>
+      </c>
+      <c r="AI72" s="101" t="s">
+        <v>2362</v>
+      </c>
+      <c r="AJ72" s="101" t="s">
+        <v>2363</v>
+      </c>
+      <c r="AK72" s="102" t="s">
+        <v>2364</v>
+      </c>
+      <c r="AL72" s="91" t="s">
+        <v>2347</v>
       </c>
       <c r="AM72" s="91" t="s">
-        <v>1775</v>
-      </c>
-      <c r="AP72" s="9"/>
-      <c r="AQ72" s="2"/>
+        <v>1791</v>
+      </c>
+      <c r="AO72" s="2"/>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="87"/>
       <c r="D73" s="1"/>
-      <c r="AL73" s="4"/>
-      <c r="AP73" s="9"/>
-      <c r="AQ73" s="2"/>
+      <c r="K73" s="73"/>
+      <c r="AC73" s="103"/>
+      <c r="AD73" s="103"/>
+      <c r="AH73" s="103"/>
+      <c r="AI73" s="103"/>
+      <c r="AJ73" s="103"/>
+      <c r="AK73" s="104"/>
+      <c r="AO73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="99" t="s">
-        <v>2317</v>
+        <v>2367</v>
       </c>
       <c r="B74" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C74" s="27" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="D74" s="1" t="n">
-        <v>106</v>
-      </c>
-      <c r="E74" s="100" t="n">
-        <v>106</v>
-      </c>
-      <c r="F74" s="27" t="s">
-        <v>67</v>
+        <v>20</v>
+      </c>
+      <c r="E74" s="27" t="n">
+        <v>20</v>
       </c>
       <c r="G74" s="89" t="s">
-        <v>2318</v>
+        <v>2368</v>
       </c>
       <c r="H74" s="89" t="s">
-        <v>651</v>
-      </c>
-      <c r="I74" s="90" t="s">
-        <v>2319</v>
+        <v>2369</v>
       </c>
       <c r="J74" s="89" t="s">
-        <v>2320</v>
-      </c>
-      <c r="K74" s="89" t="s">
-        <v>84</v>
+        <v>2370</v>
+      </c>
+      <c r="K74" s="103" t="s">
+        <v>2371</v>
       </c>
       <c r="L74" s="90" t="s">
-        <v>84</v>
+        <v>2371</v>
       </c>
       <c r="M74" s="89" t="s">
         <v>84</v>
@@ -41222,80 +41378,83 @@
       <c r="Z74" s="89" t="s">
         <v>84</v>
       </c>
+      <c r="AA74" s="89" t="s">
+        <v>84</v>
+      </c>
       <c r="AB74" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC74" s="89" t="s">
-        <v>2321</v>
-      </c>
-      <c r="AD74" s="101" t="s">
-        <v>2322</v>
-      </c>
-      <c r="AE74" s="101" t="s">
-        <v>2323</v>
+      <c r="AC74" s="103" t="s">
+        <v>2372</v>
+      </c>
+      <c r="AD74" s="103" t="s">
+        <v>2373</v>
+      </c>
+      <c r="AE74" s="89" t="s">
+        <v>2374</v>
       </c>
       <c r="AF74" s="89" t="s">
-        <v>2324</v>
+        <v>2375</v>
       </c>
       <c r="AG74" s="89" t="s">
-        <v>2325</v>
-      </c>
-      <c r="AH74" s="89" t="s">
-        <v>2326</v>
-      </c>
-      <c r="AI74" s="89" t="s">
-        <v>2327</v>
-      </c>
-      <c r="AJ74" s="101" t="s">
-        <v>2328</v>
-      </c>
-      <c r="AK74" s="102" t="s">
-        <v>2329</v>
-      </c>
-      <c r="AL74" s="4" t="s">
-        <v>2330</v>
+        <v>2376</v>
+      </c>
+      <c r="AH74" s="103" t="s">
+        <v>2377</v>
+      </c>
+      <c r="AI74" s="103" t="s">
+        <v>2378</v>
+      </c>
+      <c r="AJ74" s="103" t="s">
+        <v>2379</v>
+      </c>
+      <c r="AK74" s="104" t="s">
+        <v>2380</v>
+      </c>
+      <c r="AL74" s="91" t="s">
+        <v>2381</v>
       </c>
       <c r="AM74" s="91" t="s">
-        <v>1775</v>
-      </c>
-      <c r="AO74" s="57"/>
-      <c r="AP74" s="2"/>
+        <v>1791</v>
+      </c>
+      <c r="AO74" s="2"/>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="87"/>
       <c r="D75" s="1"/>
+      <c r="K75" s="73"/>
+      <c r="AC75" s="103"/>
       <c r="AD75" s="103"/>
-      <c r="AE75" s="103"/>
+      <c r="AH75" s="103"/>
+      <c r="AI75" s="103"/>
       <c r="AJ75" s="103"/>
       <c r="AK75" s="104"/>
-      <c r="AL75" s="4"/>
-      <c r="AO75" s="57"/>
-      <c r="AP75" s="2"/>
+      <c r="AO75" s="2"/>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="99" t="s">
-        <v>1679</v>
+        <v>2384</v>
       </c>
       <c r="B76" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C76" s="27" t="n">
-        <v>2019</v>
+      <c r="C76" s="27" t="s">
+        <v>2385</v>
       </c>
       <c r="D76" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="E76" s="100" t="n">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="E76" s="27" t="n">
+        <v>212</v>
       </c>
       <c r="F76" s="27" t="s">
-        <v>2333</v>
+        <v>84</v>
       </c>
       <c r="G76" s="89" t="s">
-        <v>663</v>
+        <v>2386</v>
       </c>
       <c r="H76" s="89" t="s">
-        <v>664</v>
+        <v>2387</v>
       </c>
       <c r="I76" s="90" t="s">
         <v>84</v>
@@ -41303,7 +41462,7 @@
       <c r="J76" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="K76" s="89" t="s">
+      <c r="K76" s="73" t="s">
         <v>84</v>
       </c>
       <c r="L76" s="90" t="s">
@@ -41337,7 +41496,7 @@
         <v>84</v>
       </c>
       <c r="V76" s="89" t="s">
-        <v>84</v>
+        <v>2388</v>
       </c>
       <c r="W76" s="89" t="s">
         <v>84</v>
@@ -41351,82 +41510,96 @@
       <c r="Z76" s="89" t="s">
         <v>84</v>
       </c>
+      <c r="AA76" s="89" t="s">
+        <v>84</v>
+      </c>
       <c r="AB76" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC76" s="89" t="s">
-        <v>2334</v>
-      </c>
-      <c r="AD76" s="89" t="s">
-        <v>2335</v>
+      <c r="AC76" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD76" s="103" t="s">
+        <v>84</v>
       </c>
       <c r="AE76" s="89" t="s">
-        <v>2336</v>
+        <v>84</v>
       </c>
       <c r="AF76" s="89" t="s">
-        <v>2337</v>
+        <v>84</v>
       </c>
       <c r="AG76" s="89" t="s">
-        <v>2338</v>
-      </c>
-      <c r="AH76" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI76" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ76" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK76" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH76" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI76" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ76" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK76" s="104" t="s">
         <v>84</v>
       </c>
       <c r="AL76" s="91" t="s">
-        <v>2339</v>
+        <v>2389</v>
       </c>
       <c r="AM76" s="91" t="s">
         <v>1791</v>
       </c>
-      <c r="AO76" s="57"/>
-      <c r="AP76" s="2"/>
+      <c r="AO76" s="2"/>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="87"/>
       <c r="D77" s="1"/>
-      <c r="AO77" s="57"/>
-      <c r="AP77" s="2"/>
+      <c r="K77" s="73"/>
+      <c r="AC77" s="103"/>
+      <c r="AD77" s="103"/>
+      <c r="AH77" s="103"/>
+      <c r="AI77" s="103"/>
+      <c r="AJ77" s="103"/>
+      <c r="AK77" s="104"/>
+      <c r="AO77" s="2"/>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="107" t="s">
-        <v>1680</v>
+      <c r="A78" s="99" t="s">
+        <v>2392</v>
       </c>
       <c r="B78" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C78" s="27" t="s">
-        <v>674</v>
+      <c r="C78" s="27" t="n">
+        <v>2021</v>
       </c>
       <c r="D78" s="1" t="n">
-        <v>3672</v>
-      </c>
-      <c r="E78" s="100" t="n">
-        <v>3982</v>
+        <v>33</v>
+      </c>
+      <c r="E78" s="27" t="n">
+        <v>255</v>
       </c>
       <c r="F78" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G78" s="89" t="s">
-        <v>2342</v>
-      </c>
-      <c r="H78" s="115" t="s">
-        <v>2343</v>
+        <v>2393</v>
+      </c>
+      <c r="H78" s="89" t="s">
+        <v>2394</v>
       </c>
       <c r="I78" s="90" t="s">
-        <v>2344</v>
-      </c>
-      <c r="J78" s="116"/>
-      <c r="K78" s="116"/>
-      <c r="L78" s="117"/>
+        <v>84</v>
+      </c>
+      <c r="J78" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="K78" s="73" t="s">
+        <v>84</v>
+      </c>
+      <c r="L78" s="90" t="s">
+        <v>84</v>
+      </c>
       <c r="M78" s="89" t="s">
         <v>84</v>
       </c>
@@ -41469,91 +41642,99 @@
       <c r="Z78" s="89" t="s">
         <v>84</v>
       </c>
+      <c r="AA78" s="89" t="s">
+        <v>84</v>
+      </c>
       <c r="AB78" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC78" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD78" s="89" t="s">
-        <v>2346</v>
+      <c r="AC78" s="103" t="s">
+        <v>2395</v>
+      </c>
+      <c r="AD78" s="103" t="s">
+        <v>2396</v>
       </c>
       <c r="AE78" s="89" t="s">
-        <v>84</v>
+        <v>2397</v>
       </c>
       <c r="AF78" s="89" t="s">
-        <v>84</v>
+        <v>2398</v>
       </c>
       <c r="AG78" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH78" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI78" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ78" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK78" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL78" s="91" t="s">
-        <v>2347</v>
+        <v>2399</v>
+      </c>
+      <c r="AH78" s="103" t="s">
+        <v>2400</v>
+      </c>
+      <c r="AI78" s="103" t="s">
+        <v>2401</v>
+      </c>
+      <c r="AJ78" s="103" t="s">
+        <v>2402</v>
+      </c>
+      <c r="AK78" s="104" t="s">
+        <v>2403</v>
+      </c>
+      <c r="AL78" s="119" t="s">
+        <v>2404</v>
       </c>
       <c r="AM78" s="91" t="s">
-        <v>1775</v>
-      </c>
-      <c r="AO78" s="9"/>
-      <c r="AP78" s="2"/>
+        <v>1791</v>
+      </c>
+      <c r="AN78" s="106"/>
+      <c r="AO78" s="2"/>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="87"/>
       <c r="D79" s="1"/>
-      <c r="J79" s="103"/>
-      <c r="K79" s="103"/>
-      <c r="L79" s="104"/>
-      <c r="AO79" s="9"/>
-      <c r="AP79" s="2"/>
+      <c r="K79" s="73"/>
+      <c r="AC79" s="103"/>
+      <c r="AD79" s="103"/>
+      <c r="AH79" s="103"/>
+      <c r="AI79" s="103"/>
+      <c r="AJ79" s="103"/>
+      <c r="AK79" s="104"/>
+      <c r="AO79" s="2"/>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="99" t="s">
-        <v>1681</v>
+        <v>2407</v>
       </c>
       <c r="B80" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C80" s="27" t="n">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D80" s="1" t="n">
-        <v>1983</v>
-      </c>
-      <c r="E80" s="100" t="n">
-        <v>1983</v>
+        <v>34</v>
+      </c>
+      <c r="E80" s="27" t="n">
+        <v>34</v>
       </c>
       <c r="F80" s="27" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="G80" s="89" t="s">
-        <v>2351</v>
+        <v>2408</v>
       </c>
       <c r="H80" s="89" t="s">
-        <v>688</v>
+        <v>2409</v>
       </c>
       <c r="I80" s="90" t="s">
-        <v>2352</v>
+        <v>84</v>
       </c>
       <c r="J80" s="89" t="s">
-        <v>2353</v>
-      </c>
-      <c r="K80" s="118"/>
+        <v>84</v>
+      </c>
+      <c r="K80" s="103" t="s">
+        <v>84</v>
+      </c>
       <c r="L80" s="90" t="s">
         <v>84</v>
       </c>
       <c r="M80" s="89" t="s">
-        <v>2355</v>
+        <v>84</v>
       </c>
       <c r="N80" s="89" t="s">
         <v>84</v>
@@ -41594,42 +41775,46 @@
       <c r="Z80" s="89" t="s">
         <v>84</v>
       </c>
+      <c r="AA80" s="89" t="s">
+        <v>84</v>
+      </c>
       <c r="AB80" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC80" s="101" t="s">
-        <v>2356</v>
-      </c>
-      <c r="AD80" s="101" t="s">
-        <v>2357</v>
+      <c r="AC80" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD80" s="103" t="s">
+        <v>84</v>
       </c>
       <c r="AE80" s="89" t="s">
-        <v>2358</v>
+        <v>84</v>
       </c>
       <c r="AF80" s="89" t="s">
-        <v>2359</v>
+        <v>84</v>
       </c>
       <c r="AG80" s="89" t="s">
-        <v>2360</v>
-      </c>
-      <c r="AH80" s="101" t="s">
-        <v>2361</v>
-      </c>
-      <c r="AI80" s="101" t="s">
-        <v>2362</v>
-      </c>
-      <c r="AJ80" s="101" t="s">
-        <v>2363</v>
-      </c>
-      <c r="AK80" s="102" t="s">
-        <v>2364</v>
+        <v>84</v>
+      </c>
+      <c r="AH80" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI80" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ80" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="AK80" s="104" t="s">
+        <v>84</v>
       </c>
       <c r="AL80" s="91" t="s">
-        <v>2347</v>
+        <v>2314</v>
       </c>
       <c r="AM80" s="91" t="s">
         <v>1791</v>
       </c>
+      <c r="AN80" s="106"/>
       <c r="AO80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -41645,47 +41830,53 @@
       <c r="AO81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="99" t="s">
-        <v>2367</v>
+      <c r="A82" s="107" t="s">
+        <v>1682</v>
       </c>
       <c r="B82" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C82" s="27" t="n">
-        <v>2019</v>
+      <c r="C82" s="27" t="s">
+        <v>703</v>
       </c>
       <c r="D82" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E82" s="27" t="n">
-        <v>20</v>
+        <v>5804</v>
+      </c>
+      <c r="E82" s="100" t="s">
+        <v>2412</v>
+      </c>
+      <c r="F82" s="27" t="s">
+        <v>114</v>
       </c>
       <c r="G82" s="89" t="s">
-        <v>2368</v>
+        <v>2413</v>
       </c>
       <c r="H82" s="89" t="s">
-        <v>2369</v>
+        <v>2679</v>
+      </c>
+      <c r="I82" s="90" t="s">
+        <v>2415</v>
       </c>
       <c r="J82" s="89" t="s">
-        <v>2370</v>
-      </c>
-      <c r="K82" s="103" t="s">
-        <v>2371</v>
+        <v>2416</v>
+      </c>
+      <c r="K82" s="89" t="s">
+        <v>2417</v>
       </c>
       <c r="L82" s="90" t="s">
-        <v>2371</v>
+        <v>84</v>
       </c>
       <c r="M82" s="89" t="s">
-        <v>84</v>
+        <v>2418</v>
       </c>
       <c r="N82" s="89" t="s">
         <v>84</v>
       </c>
       <c r="O82" s="89" t="s">
-        <v>84</v>
+        <v>2419</v>
       </c>
       <c r="P82" s="89" t="s">
-        <v>84</v>
+        <v>2420</v>
       </c>
       <c r="Q82" s="89" t="s">
         <v>84</v>
@@ -41697,7 +41888,7 @@
         <v>84</v>
       </c>
       <c r="T82" s="89" t="s">
-        <v>84</v>
+        <v>2421</v>
       </c>
       <c r="U82" s="89" t="s">
         <v>84</v>
@@ -41715,229 +41906,119 @@
         <v>84</v>
       </c>
       <c r="Z82" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA82" s="89" t="s">
-        <v>84</v>
+        <v>2422</v>
       </c>
       <c r="AB82" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC82" s="103" t="s">
-        <v>2372</v>
-      </c>
-      <c r="AD82" s="103" t="s">
-        <v>2373</v>
+      <c r="AC82" s="89" t="s">
+        <v>2423</v>
+      </c>
+      <c r="AD82" s="89" t="s">
+        <v>2424</v>
       </c>
       <c r="AE82" s="89" t="s">
-        <v>2374</v>
+        <v>2425</v>
       </c>
       <c r="AF82" s="89" t="s">
-        <v>2375</v>
+        <v>2680</v>
       </c>
       <c r="AG82" s="89" t="s">
-        <v>2376</v>
-      </c>
-      <c r="AH82" s="103" t="s">
-        <v>2377</v>
-      </c>
-      <c r="AI82" s="103" t="s">
-        <v>2378</v>
-      </c>
-      <c r="AJ82" s="103" t="s">
-        <v>2379</v>
-      </c>
-      <c r="AK82" s="104" t="s">
-        <v>2380</v>
+        <v>2427</v>
+      </c>
+      <c r="AH82" s="89" t="s">
+        <v>2428</v>
+      </c>
+      <c r="AI82" s="89" t="s">
+        <v>2429</v>
+      </c>
+      <c r="AJ82" s="89" t="s">
+        <v>2430</v>
+      </c>
+      <c r="AK82" s="90" t="s">
+        <v>2431</v>
       </c>
       <c r="AL82" s="91" t="s">
-        <v>2381</v>
+        <v>2432</v>
       </c>
       <c r="AM82" s="91" t="s">
-        <v>1791</v>
-      </c>
-      <c r="AO82" s="2"/>
+        <v>1775</v>
+      </c>
+      <c r="AO82" s="9"/>
+      <c r="AP82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="87"/>
+      <c r="A83" s="87" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>2</v>
+      </c>
       <c r="D83" s="1"/>
-      <c r="K83" s="73"/>
-      <c r="AC83" s="103"/>
-      <c r="AD83" s="103"/>
-      <c r="AH83" s="103"/>
-      <c r="AI83" s="103"/>
-      <c r="AJ83" s="103"/>
-      <c r="AK83" s="104"/>
-      <c r="AO83" s="2"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="103" t="s">
+        <v>2681</v>
+      </c>
+      <c r="I83" s="126"/>
+      <c r="AO83" s="9"/>
+      <c r="AP83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="99" t="s">
-        <v>2384</v>
+      <c r="A84" s="87" t="s">
+        <v>2436</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" s="27" t="s">
-        <v>2385</v>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="E84" s="27" t="n">
-        <v>212</v>
-      </c>
-      <c r="F84" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G84" s="89" t="s">
-        <v>2386</v>
-      </c>
-      <c r="H84" s="89" t="s">
-        <v>2387</v>
-      </c>
-      <c r="I84" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="J84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="K84" s="73" t="s">
-        <v>84</v>
-      </c>
-      <c r="L84" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="M84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="N84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="S84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V84" s="89" t="s">
-        <v>2388</v>
-      </c>
-      <c r="W84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB84" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC84" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD84" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG84" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH84" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI84" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ84" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK84" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="AL84" s="91" t="s">
-        <v>2389</v>
-      </c>
-      <c r="AM84" s="91" t="s">
-        <v>1791</v>
-      </c>
-      <c r="AO84" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D84" s="1"/>
+      <c r="H84" s="103" t="s">
+        <v>2682</v>
+      </c>
+      <c r="AO84" s="9"/>
+      <c r="AP84" s="2"/>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="87"/>
       <c r="D85" s="1"/>
-      <c r="K85" s="73"/>
-      <c r="AC85" s="103"/>
-      <c r="AD85" s="103"/>
-      <c r="AH85" s="103"/>
-      <c r="AI85" s="103"/>
-      <c r="AJ85" s="103"/>
-      <c r="AK85" s="104"/>
-      <c r="AO85" s="2"/>
+      <c r="AO85" s="9"/>
+      <c r="AP85" s="2"/>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="99" t="s">
-        <v>2392</v>
+        <v>1683</v>
       </c>
       <c r="B86" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C86" s="27" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="D86" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="E86" s="27" t="n">
-        <v>255</v>
+        <v>32</v>
+      </c>
+      <c r="E86" s="100" t="n">
+        <v>32</v>
       </c>
       <c r="F86" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G86" s="89" t="s">
-        <v>2393</v>
+        <v>2437</v>
       </c>
       <c r="H86" s="89" t="s">
-        <v>2394</v>
+        <v>776</v>
       </c>
       <c r="I86" s="90" t="s">
-        <v>84</v>
+        <v>2438</v>
       </c>
       <c r="J86" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="K86" s="73" t="s">
+        <v>2439</v>
+      </c>
+      <c r="K86" s="89" t="s">
         <v>84</v>
       </c>
       <c r="L86" s="90" t="s">
-        <v>84</v>
+        <v>2440</v>
       </c>
       <c r="M86" s="89" t="s">
         <v>84</v>
@@ -41981,84 +42062,75 @@
       <c r="Z86" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="AA86" s="89" t="s">
-        <v>84</v>
-      </c>
       <c r="AB86" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC86" s="103" t="s">
-        <v>2395</v>
-      </c>
-      <c r="AD86" s="103" t="s">
-        <v>2396</v>
-      </c>
-      <c r="AE86" s="89" t="s">
-        <v>2397</v>
+      <c r="AC86" s="89" t="s">
+        <v>2441</v>
+      </c>
+      <c r="AD86" s="89" t="s">
+        <v>2442</v>
+      </c>
+      <c r="AE86" s="101" t="s">
+        <v>2443</v>
       </c>
       <c r="AF86" s="89" t="s">
-        <v>2398</v>
+        <v>2444</v>
       </c>
       <c r="AG86" s="89" t="s">
-        <v>2399</v>
-      </c>
-      <c r="AH86" s="103" t="s">
-        <v>2400</v>
-      </c>
-      <c r="AI86" s="103" t="s">
-        <v>2401</v>
-      </c>
-      <c r="AJ86" s="103" t="s">
-        <v>2402</v>
-      </c>
-      <c r="AK86" s="104" t="s">
-        <v>2403</v>
-      </c>
-      <c r="AL86" s="119" t="s">
-        <v>2404</v>
+        <v>2445</v>
+      </c>
+      <c r="AH86" s="89" t="s">
+        <v>2446</v>
+      </c>
+      <c r="AI86" s="89" t="s">
+        <v>2447</v>
+      </c>
+      <c r="AJ86" s="89" t="s">
+        <v>2448</v>
+      </c>
+      <c r="AK86" s="120" t="s">
+        <v>2449</v>
+      </c>
+      <c r="AL86" s="91" t="s">
+        <v>2450</v>
       </c>
       <c r="AM86" s="91" t="s">
         <v>1791</v>
       </c>
-      <c r="AN86" s="106"/>
-      <c r="AO86" s="2"/>
+      <c r="AO86" s="9"/>
+      <c r="AP86" s="2"/>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="87"/>
       <c r="D87" s="1"/>
-      <c r="K87" s="73"/>
-      <c r="AC87" s="103"/>
-      <c r="AD87" s="103"/>
-      <c r="AH87" s="103"/>
-      <c r="AI87" s="103"/>
-      <c r="AJ87" s="103"/>
-      <c r="AK87" s="104"/>
-      <c r="AO87" s="2"/>
+      <c r="AO87" s="9"/>
+      <c r="AP87" s="2"/>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="99" t="s">
-        <v>2407</v>
+        <v>2453</v>
       </c>
       <c r="B88" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C88" s="27" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="E88" s="27" t="n">
-        <v>34</v>
+      <c r="C88" s="27" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D88" s="103" t="s">
+        <v>2455</v>
+      </c>
+      <c r="E88" s="100" t="n">
+        <v>197</v>
       </c>
       <c r="F88" s="27" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="G88" s="89" t="s">
-        <v>2408</v>
+        <v>2456</v>
       </c>
       <c r="H88" s="89" t="s">
-        <v>2409</v>
+        <v>2457</v>
       </c>
       <c r="I88" s="90" t="s">
         <v>84</v>
@@ -42066,7 +42138,7 @@
       <c r="J88" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="K88" s="103" t="s">
+      <c r="K88" s="89" t="s">
         <v>84</v>
       </c>
       <c r="L88" s="90" t="s">
@@ -42114,248 +42186,322 @@
       <c r="Z88" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="AA88" s="89" t="s">
-        <v>84</v>
-      </c>
       <c r="AB88" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC88" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD88" s="103" t="s">
-        <v>84</v>
+      <c r="AC88" s="89" t="s">
+        <v>2458</v>
+      </c>
+      <c r="AD88" s="89" t="s">
+        <v>2459</v>
       </c>
       <c r="AE88" s="89" t="s">
-        <v>84</v>
+        <v>2460</v>
       </c>
       <c r="AF88" s="89" t="s">
-        <v>84</v>
+        <v>2461</v>
       </c>
       <c r="AG88" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH88" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI88" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ88" s="103" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK88" s="104" t="s">
-        <v>84</v>
+        <v>2462</v>
+      </c>
+      <c r="AH88" s="89" t="s">
+        <v>2463</v>
+      </c>
+      <c r="AI88" s="89" t="s">
+        <v>2464</v>
+      </c>
+      <c r="AJ88" s="89" t="s">
+        <v>2465</v>
+      </c>
+      <c r="AK88" s="90" t="s">
+        <v>2466</v>
       </c>
       <c r="AL88" s="91" t="s">
-        <v>2314</v>
+        <v>2467</v>
       </c>
       <c r="AM88" s="91" t="s">
-        <v>1791</v>
-      </c>
-      <c r="AN88" s="106"/>
-      <c r="AO88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="87"/>
-      <c r="D89" s="1"/>
-      <c r="K89" s="73"/>
-      <c r="AC89" s="103"/>
-      <c r="AD89" s="103"/>
-      <c r="AH89" s="103"/>
-      <c r="AI89" s="103"/>
-      <c r="AJ89" s="103"/>
-      <c r="AK89" s="104"/>
-      <c r="AO89" s="2"/>
+        <v>1775</v>
+      </c>
+      <c r="AO88" s="9"/>
+      <c r="AP88" s="14"/>
+    </row>
+    <row r="89" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="99" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C89" s="121" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D89" s="103" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E89" s="27" t="n">
+        <v>153</v>
+      </c>
+      <c r="F89" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G89" s="89" t="s">
+        <v>2473</v>
+      </c>
+      <c r="AC89" s="89" t="s">
+        <v>2474</v>
+      </c>
+      <c r="AD89" s="89" t="s">
+        <v>2475</v>
+      </c>
+      <c r="AE89" s="89" t="s">
+        <v>2476</v>
+      </c>
+      <c r="AF89" s="89" t="s">
+        <v>2477</v>
+      </c>
+      <c r="AG89" s="89" t="s">
+        <v>2478</v>
+      </c>
+      <c r="AH89" s="89" t="s">
+        <v>2479</v>
+      </c>
+      <c r="AI89" s="89" t="s">
+        <v>2480</v>
+      </c>
+      <c r="AJ89" s="89" t="s">
+        <v>2481</v>
+      </c>
+      <c r="AK89" s="90" t="s">
+        <v>2482</v>
+      </c>
+      <c r="AL89" s="122" t="s">
+        <v>2483</v>
+      </c>
+      <c r="AO89" s="9"/>
+      <c r="AP89" s="14"/>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="107" t="s">
-        <v>1682</v>
+      <c r="A90" s="99" t="s">
+        <v>2484</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" s="27" t="s">
-        <v>703</v>
+        <v>2</v>
+      </c>
+      <c r="C90" s="27" t="n">
+        <v>1994</v>
       </c>
       <c r="D90" s="1" t="n">
-        <v>5804</v>
-      </c>
-      <c r="E90" s="100" t="s">
-        <v>2412</v>
+        <v>22</v>
+      </c>
+      <c r="E90" s="27" t="n">
+        <v>44</v>
       </c>
       <c r="F90" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="G90" s="89" t="s">
-        <v>2413</v>
-      </c>
-      <c r="H90" s="89" t="s">
-        <v>2414</v>
-      </c>
-      <c r="I90" s="90" t="s">
-        <v>2415</v>
-      </c>
-      <c r="J90" s="89" t="s">
-        <v>2416</v>
-      </c>
-      <c r="K90" s="89" t="s">
-        <v>2417</v>
-      </c>
-      <c r="L90" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="M90" s="89" t="s">
-        <v>2418</v>
-      </c>
-      <c r="N90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O90" s="89" t="s">
-        <v>2419</v>
-      </c>
-      <c r="P90" s="89" t="s">
-        <v>2420</v>
-      </c>
-      <c r="Q90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="S90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T90" s="89" t="s">
-        <v>2421</v>
-      </c>
-      <c r="U90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y90" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z90" s="89" t="s">
-        <v>2422</v>
-      </c>
-      <c r="AB90" s="90" t="s">
-        <v>84</v>
-      </c>
+      <c r="G90" s="1"/>
       <c r="AC90" s="89" t="s">
-        <v>2423</v>
+        <v>2485</v>
       </c>
       <c r="AD90" s="89" t="s">
-        <v>2424</v>
+        <v>2486</v>
       </c>
       <c r="AE90" s="89" t="s">
-        <v>2425</v>
+        <v>2487</v>
       </c>
       <c r="AF90" s="89" t="s">
-        <v>2678</v>
+        <v>2488</v>
       </c>
       <c r="AG90" s="89" t="s">
-        <v>2427</v>
+        <v>2489</v>
       </c>
       <c r="AH90" s="89" t="s">
-        <v>2428</v>
+        <v>2490</v>
       </c>
       <c r="AI90" s="89" t="s">
-        <v>2429</v>
+        <v>2491</v>
       </c>
       <c r="AJ90" s="89" t="s">
-        <v>2430</v>
+        <v>2492</v>
       </c>
       <c r="AK90" s="90" t="s">
-        <v>2431</v>
-      </c>
-      <c r="AL90" s="91" t="s">
-        <v>2432</v>
-      </c>
-      <c r="AM90" s="91" t="s">
+        <v>2493</v>
+      </c>
+      <c r="AL90" s="122" t="s">
+        <v>2494</v>
+      </c>
+      <c r="AO90" s="9"/>
+      <c r="AP90" s="14"/>
+    </row>
+    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AO91" s="9"/>
+      <c r="AP91" s="14"/>
+    </row>
+    <row r="92" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="99" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="27" t="s">
+        <v>798</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>461</v>
+      </c>
+      <c r="E92" s="100" t="n">
+        <v>453</v>
+      </c>
+      <c r="F92" s="27" t="s">
+        <v>114</v>
+      </c>
+      <c r="G92" s="89" t="s">
+        <v>2496</v>
+      </c>
+      <c r="H92" s="89" t="s">
+        <v>803</v>
+      </c>
+      <c r="I92" s="90" t="s">
+        <v>2497</v>
+      </c>
+      <c r="J92" s="89" t="s">
+        <v>2498</v>
+      </c>
+      <c r="K92" s="89" t="s">
+        <v>2499</v>
+      </c>
+      <c r="L92" s="90" t="s">
+        <v>2500</v>
+      </c>
+      <c r="M92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z92" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB92" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC92" s="89" t="s">
+        <v>2501</v>
+      </c>
+      <c r="AD92" s="101" t="s">
+        <v>2502</v>
+      </c>
+      <c r="AE92" s="89" t="s">
+        <v>2503</v>
+      </c>
+      <c r="AF92" s="89" t="s">
+        <v>2503</v>
+      </c>
+      <c r="AG92" s="101" t="s">
+        <v>2504</v>
+      </c>
+      <c r="AH92" s="101" t="s">
+        <v>2505</v>
+      </c>
+      <c r="AI92" s="101" t="s">
+        <v>2506</v>
+      </c>
+      <c r="AJ92" s="101" t="s">
+        <v>2507</v>
+      </c>
+      <c r="AK92" s="102" t="s">
+        <v>2508</v>
+      </c>
+      <c r="AL92" s="106" t="s">
+        <v>2509</v>
+      </c>
+      <c r="AM92" s="91" t="s">
         <v>1775</v>
       </c>
-      <c r="AO90" s="9"/>
-      <c r="AP90" s="2"/>
-    </row>
-    <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="87" t="s">
-        <v>2435</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D91" s="1"/>
-      <c r="AO91" s="9"/>
-      <c r="AP91" s="2"/>
-    </row>
-    <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="87" t="s">
-        <v>2436</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D92" s="1"/>
       <c r="AO92" s="9"/>
       <c r="AP92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="87"/>
-      <c r="D93" s="1"/>
       <c r="AO93" s="9"/>
       <c r="AP93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="99" t="s">
-        <v>1683</v>
+      <c r="A94" s="107" t="s">
+        <v>1684</v>
       </c>
       <c r="B94" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C94" s="27" t="n">
-        <v>2018</v>
+      <c r="C94" s="27" t="s">
+        <v>2511</v>
       </c>
       <c r="D94" s="1" t="n">
-        <v>32</v>
+        <v>1775</v>
       </c>
       <c r="E94" s="100" t="n">
-        <v>32</v>
+        <v>1914</v>
       </c>
       <c r="F94" s="27" t="s">
         <v>67</v>
       </c>
       <c r="G94" s="89" t="s">
-        <v>2437</v>
-      </c>
-      <c r="H94" s="89" t="s">
-        <v>776</v>
+        <v>2513</v>
+      </c>
+      <c r="H94" s="73" t="s">
+        <v>2683</v>
       </c>
       <c r="I94" s="90" t="s">
-        <v>2438</v>
+        <v>2515</v>
       </c>
       <c r="J94" s="89" t="s">
-        <v>2439</v>
+        <v>84</v>
       </c>
       <c r="K94" s="89" t="s">
         <v>84</v>
       </c>
       <c r="L94" s="90" t="s">
-        <v>2440</v>
+        <v>84</v>
       </c>
       <c r="M94" s="89" t="s">
-        <v>84</v>
+        <v>2516</v>
       </c>
       <c r="N94" s="89" t="s">
-        <v>84</v>
+        <v>2517</v>
       </c>
       <c r="O94" s="89" t="s">
         <v>84</v>
@@ -42364,19 +42510,19 @@
         <v>84</v>
       </c>
       <c r="Q94" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R94" s="89" t="s">
-        <v>84</v>
+        <v>2518</v>
+      </c>
+      <c r="R94" s="73" t="s">
+        <v>2684</v>
       </c>
       <c r="S94" s="89" t="s">
-        <v>84</v>
+        <v>2520</v>
       </c>
       <c r="T94" s="89" t="s">
-        <v>84</v>
+        <v>2521</v>
       </c>
       <c r="U94" s="89" t="s">
-        <v>84</v>
+        <v>2522</v>
       </c>
       <c r="V94" s="89" t="s">
         <v>84</v>
@@ -42397,77 +42543,77 @@
         <v>84</v>
       </c>
       <c r="AC94" s="89" t="s">
-        <v>2441</v>
+        <v>2523</v>
       </c>
       <c r="AD94" s="89" t="s">
-        <v>2442</v>
-      </c>
-      <c r="AE94" s="101" t="s">
-        <v>2443</v>
+        <v>2524</v>
+      </c>
+      <c r="AE94" s="89" t="s">
+        <v>2525</v>
       </c>
       <c r="AF94" s="89" t="s">
-        <v>2444</v>
+        <v>2526</v>
       </c>
       <c r="AG94" s="89" t="s">
-        <v>2445</v>
+        <v>2527</v>
       </c>
       <c r="AH94" s="89" t="s">
-        <v>2446</v>
+        <v>2528</v>
       </c>
       <c r="AI94" s="89" t="s">
-        <v>2447</v>
+        <v>2529</v>
       </c>
       <c r="AJ94" s="89" t="s">
-        <v>2448</v>
-      </c>
-      <c r="AK94" s="120" t="s">
-        <v>2449</v>
+        <v>2530</v>
+      </c>
+      <c r="AK94" s="90" t="s">
+        <v>2531</v>
       </c>
       <c r="AL94" s="91" t="s">
-        <v>2450</v>
+        <v>2532</v>
       </c>
       <c r="AM94" s="91" t="s">
-        <v>1791</v>
+        <v>1775</v>
       </c>
       <c r="AO94" s="9"/>
       <c r="AP94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="87"/>
-      <c r="D95" s="1"/>
+      <c r="H95" s="73"/>
+      <c r="R95" s="73"/>
       <c r="AO95" s="9"/>
       <c r="AP95" s="2"/>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="99" t="s">
-        <v>2453</v>
+        <v>1685</v>
       </c>
       <c r="B96" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C96" s="27" t="s">
-        <v>2454</v>
-      </c>
-      <c r="D96" s="103" t="s">
-        <v>2455</v>
+        <v>798</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>25</v>
       </c>
       <c r="E96" s="100" t="n">
-        <v>197</v>
+        <v>25</v>
       </c>
       <c r="F96" s="27" t="s">
         <v>114</v>
       </c>
       <c r="G96" s="89" t="s">
-        <v>2456</v>
+        <v>2535</v>
       </c>
       <c r="H96" s="89" t="s">
-        <v>2457</v>
+        <v>840</v>
       </c>
       <c r="I96" s="90" t="s">
-        <v>84</v>
+        <v>2536</v>
       </c>
       <c r="J96" s="89" t="s">
-        <v>84</v>
+        <v>2537</v>
       </c>
       <c r="K96" s="89" t="s">
         <v>84</v>
@@ -42476,7 +42622,7 @@
         <v>84</v>
       </c>
       <c r="M96" s="89" t="s">
-        <v>84</v>
+        <v>2538</v>
       </c>
       <c r="N96" s="89" t="s">
         <v>84</v>
@@ -42520,192 +42666,200 @@
       <c r="AB96" s="90" t="s">
         <v>84</v>
       </c>
-      <c r="AC96" s="89" t="s">
-        <v>2458</v>
+      <c r="AC96" s="101" t="s">
+        <v>2539</v>
       </c>
       <c r="AD96" s="89" t="s">
-        <v>2459</v>
-      </c>
-      <c r="AE96" s="89" t="s">
-        <v>2460</v>
+        <v>2540</v>
+      </c>
+      <c r="AE96" s="101" t="s">
+        <v>2541</v>
       </c>
       <c r="AF96" s="89" t="s">
-        <v>2461</v>
+        <v>2542</v>
       </c>
       <c r="AG96" s="89" t="s">
-        <v>2462</v>
+        <v>2543</v>
       </c>
       <c r="AH96" s="89" t="s">
-        <v>2463</v>
+        <v>2544</v>
       </c>
       <c r="AI96" s="89" t="s">
-        <v>2464</v>
+        <v>2545</v>
       </c>
       <c r="AJ96" s="89" t="s">
-        <v>2465</v>
+        <v>2546</v>
       </c>
       <c r="AK96" s="90" t="s">
-        <v>2466</v>
-      </c>
-      <c r="AL96" s="91" t="s">
-        <v>2467</v>
+        <v>2547</v>
+      </c>
+      <c r="AL96" s="4" t="s">
+        <v>2548</v>
       </c>
       <c r="AM96" s="91" t="s">
-        <v>1775</v>
-      </c>
+        <v>1791</v>
+      </c>
+      <c r="AN96" s="89"/>
       <c r="AO96" s="9"/>
-      <c r="AP96" s="14"/>
-    </row>
-    <row r="97" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="99" t="s">
-        <v>2470</v>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C97" s="121" t="s">
-        <v>2471</v>
-      </c>
-      <c r="D97" s="103" t="s">
-        <v>2472</v>
-      </c>
-      <c r="E97" s="27" t="n">
-        <v>153</v>
-      </c>
-      <c r="F97" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G97" s="89" t="s">
-        <v>2473</v>
-      </c>
-      <c r="AC97" s="89" t="s">
-        <v>2474</v>
-      </c>
-      <c r="AD97" s="89" t="s">
-        <v>2475</v>
-      </c>
-      <c r="AE97" s="89" t="s">
-        <v>2476</v>
-      </c>
-      <c r="AF97" s="89" t="s">
-        <v>2477</v>
-      </c>
-      <c r="AG97" s="89" t="s">
-        <v>2478</v>
-      </c>
-      <c r="AH97" s="89" t="s">
-        <v>2479</v>
-      </c>
-      <c r="AI97" s="89" t="s">
-        <v>2480</v>
-      </c>
-      <c r="AJ97" s="89" t="s">
-        <v>2481</v>
-      </c>
-      <c r="AK97" s="90" t="s">
-        <v>2482</v>
-      </c>
-      <c r="AL97" s="122" t="s">
-        <v>2483</v>
-      </c>
+      <c r="AP96" s="2"/>
+    </row>
+    <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AL97" s="4"/>
+      <c r="AN97" s="89"/>
       <c r="AO97" s="9"/>
-      <c r="AP97" s="14"/>
+      <c r="AP97" s="2"/>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="99" t="s">
-        <v>2484</v>
+      <c r="A98" s="123" t="s">
+        <v>2550</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98" s="27" t="n">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="D98" s="1" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E98" s="27" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G98" s="1"/>
-      <c r="AC98" s="89" t="s">
-        <v>2485</v>
-      </c>
-      <c r="AD98" s="89" t="s">
-        <v>2486</v>
-      </c>
-      <c r="AE98" s="89" t="s">
-        <v>2487</v>
-      </c>
-      <c r="AF98" s="89" t="s">
-        <v>2488</v>
-      </c>
-      <c r="AG98" s="89" t="s">
-        <v>2489</v>
-      </c>
-      <c r="AH98" s="89" t="s">
-        <v>2490</v>
-      </c>
-      <c r="AI98" s="89" t="s">
-        <v>2491</v>
-      </c>
-      <c r="AJ98" s="89" t="s">
-        <v>2492</v>
-      </c>
-      <c r="AK98" s="90" t="s">
-        <v>2493</v>
-      </c>
-      <c r="AL98" s="122" t="s">
-        <v>2494</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="G98" s="89" t="s">
+        <v>2551</v>
+      </c>
+      <c r="H98" s="89" t="s">
+        <v>2552</v>
+      </c>
+      <c r="I98" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="J98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="K98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L98" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="M98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R98" s="89" t="s">
+        <v>2553</v>
+      </c>
+      <c r="S98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA98" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB98" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC98" s="124" t="s">
+        <v>2554</v>
+      </c>
+      <c r="AD98" s="124" t="s">
+        <v>2555</v>
+      </c>
+      <c r="AE98" s="124" t="s">
+        <v>2556</v>
+      </c>
+      <c r="AF98" s="124" t="s">
+        <v>2557</v>
+      </c>
+      <c r="AG98" s="124" t="s">
+        <v>2558</v>
+      </c>
+      <c r="AH98" s="124" t="s">
+        <v>2559</v>
+      </c>
+      <c r="AI98" s="124" t="s">
+        <v>2560</v>
+      </c>
+      <c r="AJ98" s="124" t="s">
+        <v>2561</v>
+      </c>
+      <c r="AK98" s="125" t="s">
+        <v>2562</v>
+      </c>
+      <c r="AL98" s="4" t="s">
+        <v>2563</v>
+      </c>
+      <c r="AM98" s="91" t="s">
+        <v>1791</v>
+      </c>
+      <c r="AN98" s="106"/>
       <c r="AO98" s="9"/>
-      <c r="AP98" s="14"/>
+      <c r="AP98" s="2"/>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AL99" s="4"/>
+      <c r="AN99" s="89"/>
       <c r="AO99" s="9"/>
-      <c r="AP99" s="14"/>
-    </row>
-    <row r="100" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="99" t="s">
-        <v>2495</v>
+      <c r="AP99" s="2"/>
+    </row>
+    <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="87" t="s">
+        <v>1676</v>
       </c>
       <c r="B100" s="1" t="n">
         <v>1</v>
       </c>
       <c r="C100" s="27" t="s">
-        <v>798</v>
+        <v>857</v>
       </c>
       <c r="D100" s="1" t="n">
-        <v>461</v>
+        <v>1123</v>
       </c>
       <c r="E100" s="100" t="n">
-        <v>453</v>
+        <v>2569</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="G100" s="89" t="s">
-        <v>2496</v>
-      </c>
-      <c r="H100" s="89" t="s">
-        <v>803</v>
-      </c>
-      <c r="I100" s="90" t="s">
-        <v>2497</v>
-      </c>
-      <c r="J100" s="89" t="s">
-        <v>2498</v>
+        <v>2685</v>
       </c>
       <c r="K100" s="89" t="s">
-        <v>2499</v>
-      </c>
-      <c r="L100" s="90" t="s">
-        <v>2500</v>
-      </c>
-      <c r="M100" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L100" s="104" t="s">
         <v>84</v>
       </c>
       <c r="N100" s="89" t="s">
@@ -42716,123 +42870,152 @@
       </c>
       <c r="P100" s="89" t="s">
         <v>84</v>
-      </c>
-      <c r="Q100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="S100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z100" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB100" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC100" s="89" t="s">
-        <v>2501</v>
-      </c>
-      <c r="AD100" s="101" t="s">
-        <v>2502</v>
-      </c>
-      <c r="AE100" s="89" t="s">
-        <v>2503</v>
-      </c>
-      <c r="AF100" s="89" t="s">
-        <v>2503</v>
-      </c>
-      <c r="AG100" s="101" t="s">
-        <v>2504</v>
-      </c>
-      <c r="AH100" s="101" t="s">
-        <v>2505</v>
-      </c>
-      <c r="AI100" s="101" t="s">
-        <v>2506</v>
-      </c>
-      <c r="AJ100" s="101" t="s">
-        <v>2507</v>
-      </c>
-      <c r="AK100" s="102" t="s">
-        <v>2508</v>
-      </c>
-      <c r="AL100" s="106" t="s">
-        <v>2509</v>
       </c>
       <c r="AM100" s="91" t="s">
         <v>1775</v>
       </c>
       <c r="AO100" s="9"/>
-      <c r="AP100" s="2"/>
+      <c r="AP100" s="14"/>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="87"/>
+      <c r="A101" s="1" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C101" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>3164</v>
+      </c>
+      <c r="E101" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="G101" s="89" t="s">
+        <v>2568</v>
+      </c>
+      <c r="H101" s="89" t="s">
+        <v>2569</v>
+      </c>
+      <c r="I101" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="J101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="K101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L101" s="104" t="s">
+        <v>84</v>
+      </c>
+      <c r="M101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="N101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="S101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AE101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AF101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI101" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ101" s="89" t="s">
+        <v>84</v>
+      </c>
       <c r="AO101" s="9"/>
-      <c r="AP101" s="2"/>
-    </row>
-    <row r="102" customFormat="false" ht="16.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="107" t="s">
-        <v>1684</v>
+      <c r="AP101" s="14"/>
+    </row>
+    <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="1" t="s">
+        <v>2570</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102" s="27" t="s">
-        <v>2511</v>
+        <v>2571</v>
       </c>
       <c r="D102" s="1" t="n">
-        <v>1775</v>
-      </c>
-      <c r="E102" s="100" t="n">
-        <v>1914</v>
-      </c>
-      <c r="F102" s="27" t="s">
-        <v>67</v>
+        <v>1123</v>
       </c>
       <c r="G102" s="89" t="s">
-        <v>2513</v>
-      </c>
-      <c r="H102" s="73" t="s">
-        <v>2514</v>
+        <v>2572</v>
+      </c>
+      <c r="H102" s="89" t="s">
+        <v>861</v>
       </c>
       <c r="I102" s="90" t="s">
-        <v>2515</v>
+        <v>2573</v>
       </c>
       <c r="J102" s="89" t="s">
-        <v>84</v>
+        <v>2574</v>
       </c>
       <c r="K102" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="L102" s="90" t="s">
+      <c r="L102" s="104" t="s">
         <v>84</v>
       </c>
       <c r="M102" s="89" t="s">
-        <v>2516</v>
+        <v>2575</v>
       </c>
       <c r="N102" s="89" t="s">
-        <v>2517</v>
+        <v>84</v>
       </c>
       <c r="O102" s="89" t="s">
         <v>84</v>
@@ -42840,20 +43023,17 @@
       <c r="P102" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="Q102" s="89" t="s">
-        <v>2518</v>
-      </c>
       <c r="R102" s="73" t="s">
-        <v>2679</v>
+        <v>2686</v>
       </c>
       <c r="S102" s="89" t="s">
-        <v>2520</v>
+        <v>84</v>
       </c>
       <c r="T102" s="89" t="s">
-        <v>2521</v>
+        <v>84</v>
       </c>
       <c r="U102" s="89" t="s">
-        <v>2522</v>
+        <v>84</v>
       </c>
       <c r="V102" s="89" t="s">
         <v>84</v>
@@ -42870,90 +43050,177 @@
       <c r="Z102" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="AB102" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC102" s="89" t="s">
-        <v>2523</v>
+      <c r="AA102" s="89" t="s">
+        <v>2577</v>
+      </c>
+      <c r="AB102" s="89" t="s">
+        <v>84</v>
       </c>
       <c r="AD102" s="89" t="s">
-        <v>2524</v>
+        <v>2578</v>
       </c>
       <c r="AE102" s="89" t="s">
-        <v>2525</v>
+        <v>2579</v>
       </c>
       <c r="AF102" s="89" t="s">
-        <v>2526</v>
+        <v>2580</v>
       </c>
       <c r="AG102" s="89" t="s">
-        <v>2527</v>
+        <v>2581</v>
       </c>
       <c r="AH102" s="89" t="s">
-        <v>2528</v>
+        <v>2582</v>
       </c>
       <c r="AI102" s="89" t="s">
-        <v>2529</v>
+        <v>2583</v>
       </c>
       <c r="AJ102" s="89" t="s">
-        <v>2530</v>
+        <v>2584</v>
       </c>
       <c r="AK102" s="90" t="s">
-        <v>2531</v>
-      </c>
-      <c r="AL102" s="91" t="s">
-        <v>2532</v>
-      </c>
-      <c r="AM102" s="91" t="s">
-        <v>1775</v>
+        <v>2585</v>
       </c>
       <c r="AO102" s="9"/>
       <c r="AP102" s="2"/>
+      <c r="AT102" s="27"/>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H103" s="73"/>
-      <c r="R103" s="73"/>
+      <c r="A103" s="1" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" s="27" t="s">
+        <v>2587</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>758</v>
+      </c>
+      <c r="G103" s="89" t="s">
+        <v>2588</v>
+      </c>
+      <c r="H103" s="89" t="s">
+        <v>2589</v>
+      </c>
+      <c r="I103" s="90" t="s">
+        <v>2590</v>
+      </c>
+      <c r="J103" s="89" t="s">
+        <v>2591</v>
+      </c>
+      <c r="K103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L103" s="104" t="s">
+        <v>84</v>
+      </c>
+      <c r="M103" s="89" t="s">
+        <v>1928</v>
+      </c>
+      <c r="N103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R103" s="73" t="s">
+        <v>2687</v>
+      </c>
+      <c r="S103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA103" s="89" t="s">
+        <v>2593</v>
+      </c>
+      <c r="AB103" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD103" s="89" t="s">
+        <v>2594</v>
+      </c>
+      <c r="AE103" s="89" t="s">
+        <v>2595</v>
+      </c>
+      <c r="AF103" s="89" t="s">
+        <v>2596</v>
+      </c>
+      <c r="AG103" s="89" t="s">
+        <v>2597</v>
+      </c>
+      <c r="AH103" s="89" t="s">
+        <v>2598</v>
+      </c>
+      <c r="AI103" s="89" t="s">
+        <v>2599</v>
+      </c>
+      <c r="AJ103" s="89" t="s">
+        <v>2600</v>
+      </c>
+      <c r="AK103" s="90" t="s">
+        <v>2601</v>
+      </c>
       <c r="AO103" s="9"/>
       <c r="AP103" s="2"/>
+      <c r="AT103" s="27"/>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="99" t="s">
-        <v>1685</v>
+      <c r="A104" s="1" t="s">
+        <v>2602</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" s="27" t="s">
-        <v>798</v>
+        <v>2603</v>
       </c>
       <c r="D104" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E104" s="100" t="n">
-        <v>25</v>
-      </c>
-      <c r="F104" s="27" t="s">
-        <v>114</v>
+        <v>566</v>
       </c>
       <c r="G104" s="89" t="s">
-        <v>2535</v>
+        <v>2604</v>
       </c>
       <c r="H104" s="89" t="s">
-        <v>840</v>
+        <v>2605</v>
       </c>
       <c r="I104" s="90" t="s">
-        <v>2536</v>
+        <v>2606</v>
       </c>
       <c r="J104" s="89" t="s">
-        <v>2537</v>
+        <v>2607</v>
       </c>
       <c r="K104" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="L104" s="90" t="s">
+      <c r="L104" s="104" t="s">
         <v>84</v>
       </c>
       <c r="M104" s="89" t="s">
-        <v>2538</v>
+        <v>2608</v>
       </c>
       <c r="N104" s="89" t="s">
         <v>84</v>
@@ -42964,11 +43231,8 @@
       <c r="P104" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="Q104" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R104" s="89" t="s">
-        <v>84</v>
+      <c r="R104" s="73" t="s">
+        <v>2688</v>
       </c>
       <c r="S104" s="89" t="s">
         <v>84</v>
@@ -42994,91 +43258,177 @@
       <c r="Z104" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="AB104" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC104" s="101" t="s">
-        <v>2539</v>
+      <c r="AA104" s="89" t="s">
+        <v>2610</v>
+      </c>
+      <c r="AB104" s="89" t="s">
+        <v>84</v>
       </c>
       <c r="AD104" s="89" t="s">
-        <v>2540</v>
-      </c>
-      <c r="AE104" s="101" t="s">
-        <v>2541</v>
+        <v>2611</v>
+      </c>
+      <c r="AE104" s="89" t="s">
+        <v>2612</v>
       </c>
       <c r="AF104" s="89" t="s">
-        <v>2542</v>
+        <v>2613</v>
       </c>
       <c r="AG104" s="89" t="s">
-        <v>2543</v>
+        <v>2614</v>
       </c>
       <c r="AH104" s="89" t="s">
-        <v>2544</v>
+        <v>2615</v>
       </c>
       <c r="AI104" s="89" t="s">
-        <v>2545</v>
+        <v>2616</v>
       </c>
       <c r="AJ104" s="89" t="s">
-        <v>2546</v>
+        <v>2617</v>
       </c>
       <c r="AK104" s="90" t="s">
-        <v>2547</v>
-      </c>
-      <c r="AL104" s="4" t="s">
-        <v>2548</v>
-      </c>
-      <c r="AM104" s="91" t="s">
-        <v>1791</v>
-      </c>
-      <c r="AN104" s="89"/>
+        <v>2618</v>
+      </c>
       <c r="AO104" s="9"/>
       <c r="AP104" s="2"/>
+      <c r="AT104" s="27"/>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AL105" s="4"/>
-      <c r="AN105" s="89"/>
+      <c r="A105" s="1" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="C105" s="27" t="s">
+        <v>2620</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="G105" s="89" t="s">
+        <v>2621</v>
+      </c>
+      <c r="H105" s="89" t="s">
+        <v>2622</v>
+      </c>
+      <c r="I105" s="90" t="s">
+        <v>2623</v>
+      </c>
+      <c r="J105" s="89" t="s">
+        <v>2624</v>
+      </c>
+      <c r="K105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="L105" s="104" t="s">
+        <v>84</v>
+      </c>
+      <c r="M105" s="89" t="s">
+        <v>2625</v>
+      </c>
+      <c r="N105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="O105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="P105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="R105" s="73" t="s">
+        <v>2689</v>
+      </c>
+      <c r="S105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="T105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="U105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="V105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="W105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="X105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="Z105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AA105" s="89" t="s">
+        <v>2627</v>
+      </c>
+      <c r="AB105" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD105" s="89" t="s">
+        <v>2628</v>
+      </c>
+      <c r="AE105" s="89" t="s">
+        <v>2629</v>
+      </c>
+      <c r="AF105" s="89" t="s">
+        <v>2630</v>
+      </c>
+      <c r="AG105" s="89" t="s">
+        <v>2631</v>
+      </c>
+      <c r="AH105" s="89" t="s">
+        <v>2632</v>
+      </c>
+      <c r="AI105" s="89" t="s">
+        <v>2633</v>
+      </c>
+      <c r="AJ105" s="89" t="s">
+        <v>2634</v>
+      </c>
+      <c r="AK105" s="90" t="s">
+        <v>2635</v>
+      </c>
       <c r="AO105" s="9"/>
       <c r="AP105" s="2"/>
+      <c r="AT105" s="27"/>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="123" t="s">
-        <v>2550</v>
+      <c r="A106" s="1" t="s">
+        <v>2636</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="27" t="n">
-        <v>2024</v>
+        <v>2015</v>
       </c>
       <c r="D106" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E106" s="27" t="n">
-        <v>19</v>
-      </c>
-      <c r="F106" s="27" t="s">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="G106" s="89" t="s">
-        <v>2551</v>
+        <v>2637</v>
       </c>
       <c r="H106" s="89" t="s">
-        <v>2552</v>
+        <v>2638</v>
       </c>
       <c r="I106" s="90" t="s">
-        <v>84</v>
+        <v>2639</v>
       </c>
       <c r="J106" s="89" t="s">
-        <v>84</v>
+        <v>2640</v>
       </c>
       <c r="K106" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="L106" s="90" t="s">
+      <c r="L106" s="104" t="s">
         <v>84</v>
       </c>
       <c r="M106" s="89" t="s">
-        <v>84</v>
+        <v>2641</v>
       </c>
       <c r="N106" s="89" t="s">
         <v>84</v>
@@ -43089,11 +43439,8 @@
       <c r="P106" s="89" t="s">
         <v>84</v>
       </c>
-      <c r="Q106" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R106" s="89" t="s">
-        <v>2553</v>
+      <c r="R106" s="73" t="s">
+        <v>2690</v>
       </c>
       <c r="S106" s="89" t="s">
         <v>84</v>
@@ -43120,885 +43467,215 @@
         <v>84</v>
       </c>
       <c r="AA106" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB106" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="AC106" s="124" t="s">
-        <v>2554</v>
-      </c>
-      <c r="AD106" s="124" t="s">
-        <v>2555</v>
-      </c>
-      <c r="AE106" s="124" t="s">
-        <v>2556</v>
-      </c>
-      <c r="AF106" s="124" t="s">
-        <v>2557</v>
-      </c>
-      <c r="AG106" s="124" t="s">
-        <v>2558</v>
-      </c>
-      <c r="AH106" s="124" t="s">
-        <v>2559</v>
-      </c>
-      <c r="AI106" s="124" t="s">
-        <v>2560</v>
-      </c>
-      <c r="AJ106" s="124" t="s">
-        <v>2561</v>
-      </c>
-      <c r="AK106" s="125" t="s">
-        <v>2562</v>
-      </c>
-      <c r="AL106" s="4" t="s">
-        <v>2563</v>
-      </c>
-      <c r="AM106" s="91" t="s">
-        <v>1791</v>
-      </c>
-      <c r="AN106" s="106"/>
+        <v>2643</v>
+      </c>
+      <c r="AB106" s="89" t="s">
+        <v>84</v>
+      </c>
+      <c r="AD106" s="89" t="s">
+        <v>2644</v>
+      </c>
+      <c r="AE106" s="89" t="s">
+        <v>2645</v>
+      </c>
+      <c r="AF106" s="89" t="s">
+        <v>2646</v>
+      </c>
+      <c r="AG106" s="89" t="s">
+        <v>2647</v>
+      </c>
+      <c r="AH106" s="89" t="s">
+        <v>2648</v>
+      </c>
+      <c r="AI106" s="89" t="s">
+        <v>2649</v>
+      </c>
+      <c r="AJ106" s="89" t="s">
+        <v>2650</v>
+      </c>
+      <c r="AK106" s="90" t="s">
+        <v>2651</v>
+      </c>
       <c r="AO106" s="9"/>
       <c r="AP106" s="2"/>
+      <c r="AS106" s="2"/>
+      <c r="AT106" s="27"/>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AL107" s="4"/>
-      <c r="AN107" s="89"/>
       <c r="AO107" s="9"/>
       <c r="AP107" s="2"/>
+      <c r="AS107" s="2"/>
+      <c r="AT107" s="27"/>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="87" t="s">
-        <v>1676</v>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C108" s="27" t="s">
-        <v>857</v>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>1123</v>
-      </c>
-      <c r="E108" s="100" t="n">
-        <v>2569</v>
-      </c>
-      <c r="F108" s="27" t="s">
-        <v>2680</v>
-      </c>
-      <c r="K108" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L108" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="N108" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O108" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P108" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AM108" s="91" t="s">
-        <v>1775</v>
-      </c>
+      <c r="N108" s="93"/>
+      <c r="O108" s="93"/>
+      <c r="P108" s="93"/>
+      <c r="Q108" s="93"/>
+      <c r="R108" s="93"/>
+      <c r="S108" s="93"/>
+      <c r="T108" s="93"/>
       <c r="AO108" s="9"/>
-      <c r="AP108" s="14"/>
+      <c r="AP108" s="2"/>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
-        <v>2567</v>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C109" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D109" s="1" t="n">
-        <v>3164</v>
-      </c>
-      <c r="E109" s="27" t="s">
-        <v>84</v>
-      </c>
-      <c r="G109" s="89" t="s">
-        <v>2568</v>
-      </c>
-      <c r="H109" s="89" t="s">
-        <v>2569</v>
-      </c>
-      <c r="I109" s="90" t="s">
-        <v>84</v>
-      </c>
-      <c r="J109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="K109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L109" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="M109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="N109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="S109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AB109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AE109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AF109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AG109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AH109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AI109" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AJ109" s="89" t="s">
-        <v>84</v>
-      </c>
       <c r="AO109" s="9"/>
-      <c r="AP109" s="14"/>
+      <c r="AP109" s="2"/>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
-        <v>2570</v>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C110" s="27" t="s">
-        <v>2571</v>
-      </c>
-      <c r="D110" s="1" t="n">
-        <v>1123</v>
-      </c>
-      <c r="G110" s="89" t="s">
-        <v>2572</v>
-      </c>
-      <c r="H110" s="89" t="s">
-        <v>861</v>
-      </c>
-      <c r="I110" s="90" t="s">
-        <v>2573</v>
-      </c>
-      <c r="J110" s="89" t="s">
-        <v>2574</v>
-      </c>
-      <c r="K110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L110" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="M110" s="89" t="s">
-        <v>2575</v>
-      </c>
-      <c r="N110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R110" s="73" t="s">
-        <v>2681</v>
-      </c>
-      <c r="S110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA110" s="89" t="s">
-        <v>2577</v>
-      </c>
-      <c r="AB110" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD110" s="89" t="s">
-        <v>2578</v>
-      </c>
-      <c r="AE110" s="89" t="s">
-        <v>2579</v>
-      </c>
-      <c r="AF110" s="89" t="s">
-        <v>2580</v>
-      </c>
-      <c r="AG110" s="89" t="s">
-        <v>2581</v>
-      </c>
-      <c r="AH110" s="89" t="s">
-        <v>2582</v>
-      </c>
-      <c r="AI110" s="89" t="s">
-        <v>2583</v>
-      </c>
-      <c r="AJ110" s="89" t="s">
-        <v>2584</v>
-      </c>
-      <c r="AK110" s="90" t="s">
-        <v>2585</v>
-      </c>
+      <c r="A110" s="2"/>
+      <c r="B110" s="2"/>
       <c r="AO110" s="9"/>
       <c r="AP110" s="2"/>
-      <c r="AT110" s="27"/>
     </row>
     <row r="111" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
-        <v>2586</v>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C111" s="27" t="s">
-        <v>2587</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>758</v>
-      </c>
-      <c r="G111" s="89" t="s">
-        <v>2588</v>
-      </c>
-      <c r="H111" s="89" t="s">
-        <v>2589</v>
-      </c>
-      <c r="I111" s="90" t="s">
-        <v>2590</v>
-      </c>
-      <c r="J111" s="89" t="s">
-        <v>2591</v>
-      </c>
-      <c r="K111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L111" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="M111" s="89" t="s">
-        <v>1928</v>
-      </c>
-      <c r="N111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R111" s="73" t="s">
-        <v>2682</v>
-      </c>
-      <c r="S111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA111" s="89" t="s">
-        <v>2593</v>
-      </c>
-      <c r="AB111" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD111" s="89" t="s">
-        <v>2594</v>
-      </c>
-      <c r="AE111" s="89" t="s">
-        <v>2595</v>
-      </c>
-      <c r="AF111" s="89" t="s">
-        <v>2596</v>
-      </c>
-      <c r="AG111" s="89" t="s">
-        <v>2597</v>
-      </c>
-      <c r="AH111" s="89" t="s">
-        <v>2598</v>
-      </c>
-      <c r="AI111" s="89" t="s">
-        <v>2599</v>
-      </c>
-      <c r="AJ111" s="89" t="s">
-        <v>2600</v>
-      </c>
-      <c r="AK111" s="90" t="s">
-        <v>2601</v>
-      </c>
       <c r="AO111" s="9"/>
       <c r="AP111" s="2"/>
-      <c r="AT111" s="27"/>
     </row>
     <row r="112" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
-        <v>2602</v>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C112" s="27" t="s">
-        <v>2603</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>566</v>
-      </c>
-      <c r="G112" s="89" t="s">
-        <v>2604</v>
-      </c>
-      <c r="H112" s="89" t="s">
-        <v>2605</v>
-      </c>
-      <c r="I112" s="90" t="s">
-        <v>2606</v>
-      </c>
-      <c r="J112" s="89" t="s">
-        <v>2607</v>
-      </c>
-      <c r="K112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L112" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="M112" s="89" t="s">
-        <v>2608</v>
-      </c>
-      <c r="N112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R112" s="73" t="s">
-        <v>2683</v>
-      </c>
-      <c r="S112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA112" s="89" t="s">
-        <v>2610</v>
-      </c>
-      <c r="AB112" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD112" s="89" t="s">
-        <v>2611</v>
-      </c>
-      <c r="AE112" s="89" t="s">
-        <v>2612</v>
-      </c>
-      <c r="AF112" s="89" t="s">
-        <v>2613</v>
-      </c>
-      <c r="AG112" s="89" t="s">
-        <v>2614</v>
-      </c>
-      <c r="AH112" s="89" t="s">
-        <v>2615</v>
-      </c>
-      <c r="AI112" s="89" t="s">
-        <v>2616</v>
-      </c>
-      <c r="AJ112" s="89" t="s">
-        <v>2617</v>
-      </c>
-      <c r="AK112" s="90" t="s">
-        <v>2618</v>
-      </c>
       <c r="AO112" s="9"/>
       <c r="AP112" s="2"/>
-      <c r="AT112" s="27"/>
     </row>
     <row r="113" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
-        <v>2619</v>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C113" s="27" t="s">
-        <v>2620</v>
-      </c>
-      <c r="D113" s="1" t="n">
-        <v>121</v>
-      </c>
-      <c r="G113" s="89" t="s">
-        <v>2621</v>
-      </c>
-      <c r="H113" s="89" t="s">
-        <v>2622</v>
-      </c>
-      <c r="I113" s="90" t="s">
-        <v>2623</v>
-      </c>
-      <c r="J113" s="89" t="s">
-        <v>2624</v>
-      </c>
-      <c r="K113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L113" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="M113" s="89" t="s">
-        <v>2625</v>
-      </c>
-      <c r="N113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R113" s="73" t="s">
-        <v>2684</v>
-      </c>
-      <c r="S113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA113" s="89" t="s">
-        <v>2627</v>
-      </c>
-      <c r="AB113" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD113" s="89" t="s">
-        <v>2628</v>
-      </c>
-      <c r="AE113" s="89" t="s">
-        <v>2629</v>
-      </c>
-      <c r="AF113" s="89" t="s">
-        <v>2630</v>
-      </c>
-      <c r="AG113" s="89" t="s">
-        <v>2631</v>
-      </c>
-      <c r="AH113" s="89" t="s">
-        <v>2632</v>
-      </c>
-      <c r="AI113" s="89" t="s">
-        <v>2633</v>
-      </c>
-      <c r="AJ113" s="89" t="s">
-        <v>2634</v>
-      </c>
-      <c r="AK113" s="90" t="s">
-        <v>2635</v>
-      </c>
       <c r="AO113" s="9"/>
       <c r="AP113" s="2"/>
-      <c r="AT113" s="27"/>
     </row>
     <row r="114" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
-        <v>2636</v>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="C114" s="27" t="n">
-        <v>2015</v>
-      </c>
-      <c r="D114" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G114" s="89" t="s">
-        <v>2637</v>
-      </c>
-      <c r="H114" s="89" t="s">
-        <v>2638</v>
-      </c>
-      <c r="I114" s="90" t="s">
-        <v>2639</v>
-      </c>
-      <c r="J114" s="89" t="s">
-        <v>2640</v>
-      </c>
-      <c r="K114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="L114" s="104" t="s">
-        <v>84</v>
-      </c>
-      <c r="M114" s="89" t="s">
-        <v>2641</v>
-      </c>
-      <c r="N114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="O114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="P114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="R114" s="73" t="s">
-        <v>2685</v>
-      </c>
-      <c r="S114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="T114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="U114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="V114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="W114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="X114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Y114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AA114" s="89" t="s">
-        <v>2643</v>
-      </c>
-      <c r="AB114" s="89" t="s">
-        <v>84</v>
-      </c>
-      <c r="AD114" s="89" t="s">
-        <v>2644</v>
-      </c>
-      <c r="AE114" s="89" t="s">
-        <v>2645</v>
-      </c>
-      <c r="AF114" s="89" t="s">
-        <v>2646</v>
-      </c>
-      <c r="AG114" s="89" t="s">
-        <v>2647</v>
-      </c>
-      <c r="AH114" s="89" t="s">
-        <v>2648</v>
-      </c>
-      <c r="AI114" s="89" t="s">
-        <v>2649</v>
-      </c>
-      <c r="AJ114" s="89" t="s">
-        <v>2650</v>
-      </c>
-      <c r="AK114" s="90" t="s">
-        <v>2651</v>
-      </c>
-      <c r="AO114" s="9"/>
+      <c r="E114" s="113"/>
+      <c r="G114" s="93"/>
+      <c r="H114" s="1"/>
       <c r="AP114" s="2"/>
-      <c r="AS114" s="2"/>
-      <c r="AT114" s="27"/>
     </row>
     <row r="115" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E115" s="113"/>
+      <c r="G115" s="93"/>
+      <c r="H115" s="93"/>
+      <c r="I115" s="94"/>
+      <c r="J115" s="93"/>
+      <c r="K115" s="93"/>
       <c r="AO115" s="9"/>
       <c r="AP115" s="2"/>
-      <c r="AS115" s="2"/>
-      <c r="AT115" s="27"/>
-    </row>
-    <row r="116" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N116" s="93"/>
-      <c r="O116" s="93"/>
-      <c r="P116" s="93"/>
-      <c r="Q116" s="93"/>
-      <c r="R116" s="93"/>
-      <c r="S116" s="93"/>
-      <c r="T116" s="93"/>
+    </row>
+    <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D116" s="89"/>
+      <c r="E116" s="88"/>
+      <c r="G116" s="27"/>
+      <c r="H116" s="27"/>
+      <c r="I116" s="126"/>
+      <c r="J116" s="27"/>
+      <c r="K116" s="27"/>
       <c r="AO116" s="9"/>
       <c r="AP116" s="2"/>
     </row>
-    <row r="117" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D117" s="89"/>
+      <c r="E117" s="89"/>
+      <c r="G117" s="27"/>
+      <c r="H117" s="27"/>
+      <c r="I117" s="126"/>
+      <c r="J117" s="27"/>
+      <c r="L117" s="3"/>
       <c r="AO117" s="9"/>
-      <c r="AP117" s="2"/>
-    </row>
-    <row r="118" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="AO118" s="9"/>
-      <c r="AP118" s="2"/>
-    </row>
-    <row r="119" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AO119" s="9"/>
-      <c r="AP119" s="2"/>
-    </row>
-    <row r="120" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AO120" s="9"/>
-      <c r="AP120" s="2"/>
-    </row>
-    <row r="121" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AO121" s="9"/>
-      <c r="AP121" s="2"/>
-    </row>
-    <row r="122" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E122" s="113"/>
-      <c r="G122" s="93"/>
-      <c r="H122" s="1"/>
-      <c r="AP122" s="2"/>
+      <c r="AP117" s="21"/>
+    </row>
+    <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D118" s="89"/>
+      <c r="E118" s="89"/>
+      <c r="G118" s="27"/>
+      <c r="H118" s="27"/>
+      <c r="I118" s="126"/>
+      <c r="L118" s="3"/>
+    </row>
+    <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D119" s="89"/>
+      <c r="G119" s="27"/>
+      <c r="H119" s="27"/>
+      <c r="I119" s="126"/>
+      <c r="J119" s="27"/>
+      <c r="L119" s="3"/>
+    </row>
+    <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D120" s="89"/>
+      <c r="E120" s="89"/>
+      <c r="G120" s="27"/>
+      <c r="H120" s="27"/>
+      <c r="I120" s="126"/>
+      <c r="L120" s="3"/>
+    </row>
+    <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D121" s="89"/>
+      <c r="E121" s="89"/>
+      <c r="G121" s="27"/>
+      <c r="H121" s="27"/>
+      <c r="I121" s="126"/>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D122" s="89"/>
+      <c r="E122" s="89"/>
+      <c r="G122" s="27"/>
+      <c r="H122" s="27"/>
+      <c r="I122" s="126"/>
     </row>
     <row r="123" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E123" s="113"/>
-      <c r="G123" s="93"/>
-      <c r="H123" s="93"/>
-      <c r="I123" s="94"/>
-      <c r="J123" s="93"/>
-      <c r="K123" s="93"/>
-      <c r="AO123" s="9"/>
-      <c r="AP123" s="2"/>
-    </row>
-    <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D123" s="89"/>
+      <c r="G123" s="27"/>
+      <c r="H123" s="27"/>
+      <c r="I123" s="126"/>
+    </row>
+    <row r="124" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D124" s="89"/>
-      <c r="E124" s="88"/>
       <c r="G124" s="27"/>
       <c r="H124" s="27"/>
       <c r="I124" s="126"/>
-      <c r="J124" s="27"/>
-      <c r="K124" s="27"/>
-      <c r="AO124" s="9"/>
-      <c r="AP124" s="2"/>
-    </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D125" s="89"/>
-      <c r="E125" s="89"/>
+    </row>
+    <row r="125" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G125" s="27"/>
       <c r="H125" s="27"/>
       <c r="I125" s="126"/>
-      <c r="J125" s="27"/>
-      <c r="L125" s="3"/>
-      <c r="AO125" s="9"/>
-      <c r="AP125" s="21"/>
-    </row>
-    <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D126" s="89"/>
-      <c r="E126" s="89"/>
+    </row>
+    <row r="126" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G126" s="27"/>
       <c r="H126" s="27"/>
       <c r="I126" s="126"/>
-      <c r="L126" s="3"/>
-    </row>
-    <row r="127" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D127" s="89"/>
+    </row>
+    <row r="127" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G127" s="27"/>
       <c r="H127" s="27"/>
       <c r="I127" s="126"/>
-      <c r="J127" s="27"/>
-      <c r="L127" s="3"/>
-    </row>
-    <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D128" s="89"/>
-      <c r="E128" s="89"/>
+    </row>
+    <row r="128" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G128" s="27"/>
       <c r="H128" s="27"/>
       <c r="I128" s="126"/>
-      <c r="L128" s="3"/>
-    </row>
-    <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D129" s="89"/>
-      <c r="E129" s="89"/>
+    </row>
+    <row r="129" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G129" s="27"/>
       <c r="H129" s="27"/>
       <c r="I129" s="126"/>
     </row>
-    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D130" s="89"/>
-      <c r="E130" s="89"/>
+    <row r="130" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G130" s="27"/>
       <c r="H130" s="27"/>
       <c r="I130" s="126"/>
     </row>
     <row r="131" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D131" s="89"/>
       <c r="G131" s="27"/>
       <c r="H131" s="27"/>
       <c r="I131" s="126"/>
     </row>
     <row r="132" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D132" s="89"/>
       <c r="G132" s="27"/>
       <c r="H132" s="27"/>
       <c r="I132" s="126"/>
     </row>
-    <row r="133" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G133" s="27"/>
-      <c r="H133" s="27"/>
-      <c r="I133" s="126"/>
-    </row>
-    <row r="134" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G134" s="27"/>
-      <c r="H134" s="27"/>
-      <c r="I134" s="126"/>
-    </row>
-    <row r="135" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G135" s="27"/>
-      <c r="H135" s="27"/>
-      <c r="I135" s="126"/>
-    </row>
-    <row r="136" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G136" s="27"/>
-      <c r="H136" s="27"/>
-      <c r="I136" s="126"/>
-    </row>
-    <row r="137" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G137" s="27"/>
-      <c r="H137" s="27"/>
-      <c r="I137" s="126"/>
-    </row>
-    <row r="138" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G138" s="27"/>
-      <c r="H138" s="27"/>
-      <c r="I138" s="126"/>
-    </row>
-    <row r="139" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G139" s="27"/>
-      <c r="H139" s="27"/>
-      <c r="I139" s="126"/>
-    </row>
-    <row r="140" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="G140" s="27"/>
-      <c r="H140" s="27"/>
-      <c r="I140" s="126"/>
-    </row>
+    <row r="1048568" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048569" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048570" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -44050,25 +43727,25 @@
   <sheetData>
     <row r="1" s="127" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B1" s="128" t="s">
-        <v>2686</v>
+        <v>2691</v>
       </c>
       <c r="C1" s="128"/>
       <c r="D1" s="128"/>
       <c r="E1" s="128" t="s">
-        <v>2687</v>
+        <v>2692</v>
       </c>
       <c r="F1" s="128"/>
       <c r="G1" s="128"/>
       <c r="H1" s="128"/>
       <c r="I1" s="128" t="s">
-        <v>2688</v>
+        <v>2693</v>
       </c>
       <c r="J1" s="128"/>
       <c r="K1" s="128"/>
       <c r="L1" s="128"/>
       <c r="M1" s="128"/>
       <c r="N1" s="128" t="s">
-        <v>2689</v>
+        <v>2694</v>
       </c>
       <c r="O1" s="128"/>
       <c r="P1" s="128"/>
@@ -44080,11 +43757,11 @@
       <c r="T1" s="128"/>
       <c r="U1" s="128"/>
       <c r="V1" s="128" t="s">
-        <v>2690</v>
+        <v>2695</v>
       </c>
       <c r="W1" s="128"/>
       <c r="X1" s="128" t="s">
-        <v>2691</v>
+        <v>2696</v>
       </c>
       <c r="Y1" s="128"/>
       <c r="Z1" s="128"/>
@@ -44097,16 +43774,16 @@
         <v>1560</v>
       </c>
       <c r="C2" s="89" t="s">
-        <v>2692</v>
+        <v>2697</v>
       </c>
       <c r="D2" s="90" t="s">
-        <v>2693</v>
+        <v>2698</v>
       </c>
       <c r="E2" s="89" t="s">
         <v>134</v>
       </c>
       <c r="F2" s="89" t="s">
-        <v>2694</v>
+        <v>2699</v>
       </c>
       <c r="G2" s="89" t="s">
         <v>361</v>
@@ -44115,58 +43792,58 @@
         <v>1064</v>
       </c>
       <c r="I2" s="89" t="s">
-        <v>2695</v>
+        <v>2700</v>
       </c>
       <c r="J2" s="89" t="s">
-        <v>2696</v>
+        <v>2701</v>
       </c>
       <c r="K2" s="89" t="s">
-        <v>2697</v>
+        <v>2702</v>
       </c>
       <c r="L2" s="73" t="s">
-        <v>2698</v>
+        <v>2703</v>
       </c>
       <c r="M2" s="90" t="s">
-        <v>2699</v>
+        <v>2704</v>
       </c>
       <c r="N2" s="89" t="s">
         <v>61</v>
       </c>
       <c r="O2" s="89" t="s">
-        <v>2700</v>
+        <v>2705</v>
       </c>
       <c r="P2" s="90" t="s">
-        <v>2701</v>
+        <v>2706</v>
       </c>
       <c r="Q2" s="89" t="s">
-        <v>2702</v>
+        <v>2707</v>
       </c>
       <c r="R2" s="89" t="s">
-        <v>2703</v>
+        <v>2708</v>
       </c>
       <c r="S2" s="89" t="s">
-        <v>2704</v>
+        <v>2709</v>
       </c>
       <c r="T2" s="89" t="s">
-        <v>2705</v>
+        <v>2710</v>
       </c>
       <c r="U2" s="90" t="s">
         <v>892</v>
       </c>
       <c r="V2" s="89" t="s">
-        <v>2706</v>
+        <v>2711</v>
       </c>
       <c r="W2" s="90" t="s">
         <v>52</v>
       </c>
       <c r="X2" s="89" t="s">
-        <v>2707</v>
+        <v>2712</v>
       </c>
       <c r="Y2" s="89" t="s">
         <v>1189</v>
       </c>
       <c r="Z2" s="89" t="s">
-        <v>2708</v>
+        <v>2713</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44180,16 +43857,16 @@
         <v>2</v>
       </c>
       <c r="D3" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E3" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F3" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="G3" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I3" s="89" t="n">
         <v>1</v>
@@ -44198,7 +43875,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="M3" s="90" t="n">
         <v>1</v>
@@ -44207,10 +43884,10 @@
         <v>1</v>
       </c>
       <c r="P3" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q3" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U3" s="90" t="n">
         <v>2</v>
@@ -44236,7 +43913,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E4" s="89" t="n">
         <v>1</v>
@@ -44245,7 +43922,7 @@
         <v>2</v>
       </c>
       <c r="W4" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44253,7 +43930,7 @@
         <v>1794</v>
       </c>
       <c r="B5" s="89" t="s">
-        <v>2712</v>
+        <v>2717</v>
       </c>
       <c r="C5" s="89" t="n">
         <v>2</v>
@@ -44265,49 +43942,49 @@
         <v>1</v>
       </c>
       <c r="G5" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I5" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="J5" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="K5" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="L5" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="M5" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N5" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="O5" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q5" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U5" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="V5" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W5" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="X5" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Y5" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Z5" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44315,37 +43992,37 @@
         <v>1809</v>
       </c>
       <c r="B6" s="89" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C6" s="89" t="s">
         <v>2714</v>
       </c>
-      <c r="C6" s="89" t="s">
-        <v>2709</v>
-      </c>
       <c r="D6" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E6" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G6" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I6" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J6" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K6" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M6" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N6" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q6" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44353,34 +44030,34 @@
         <v>1830</v>
       </c>
       <c r="E7" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F7" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="I7" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J7" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K7" s="89" t="s">
-        <v>2714</v>
+        <v>2719</v>
       </c>
       <c r="M7" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N7" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="S7" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U7" s="90" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Z7" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44388,28 +44065,28 @@
         <v>1844</v>
       </c>
       <c r="B8" s="89" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C8" s="89" t="s">
+        <v>2721</v>
+      </c>
+      <c r="D8" s="90" t="s">
         <v>2715</v>
       </c>
-      <c r="C8" s="89" t="s">
+      <c r="G8" s="89" t="s">
         <v>2716</v>
       </c>
-      <c r="D8" s="90" t="s">
-        <v>2710</v>
-      </c>
-      <c r="G8" s="89" t="s">
-        <v>2711</v>
-      </c>
       <c r="J8" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="K8" s="89" t="s">
+        <v>2722</v>
+      </c>
+      <c r="N8" s="89" t="s">
+        <v>2715</v>
+      </c>
+      <c r="T8" s="89" t="s">
         <v>2717</v>
-      </c>
-      <c r="N8" s="89" t="s">
-        <v>2710</v>
-      </c>
-      <c r="T8" s="89" t="s">
-        <v>2712</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44438,7 +44115,7 @@
         <v>1</v>
       </c>
       <c r="K9" s="89" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="N9" s="89" t="n">
         <v>1</v>
@@ -44447,10 +44124,10 @@
         <v>2</v>
       </c>
       <c r="U9" s="90" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="V9" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44458,49 +44135,49 @@
         <v>1873</v>
       </c>
       <c r="B10" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C10" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D10" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E10" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="F10" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G10" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="I10" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J10" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K10" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="M10" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N10" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="P10" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q10" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U10" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W10" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44508,49 +44185,49 @@
         <v>1894</v>
       </c>
       <c r="B11" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C11" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D11" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E11" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F11" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="G11" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I11" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J11" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K11" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M11" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N11" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="P11" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q11" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U11" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W11" s="90" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44563,49 +44240,49 @@
         <v>1935</v>
       </c>
       <c r="B13" s="89" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C13" s="89" t="s">
         <v>2714</v>
       </c>
-      <c r="C13" s="89" t="s">
-        <v>2709</v>
-      </c>
       <c r="D13" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K13" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="M13" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="N13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q13" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="S13" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U13" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W13" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44618,16 +44295,16 @@
         <v>1967</v>
       </c>
       <c r="B15" s="89" t="s">
-        <v>2718</v>
+        <v>2723</v>
       </c>
       <c r="C15" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D15" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E15" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44635,16 +44312,16 @@
         <v>1982</v>
       </c>
       <c r="B16" s="89" t="s">
+        <v>2720</v>
+      </c>
+      <c r="C16" s="89" t="s">
+        <v>2714</v>
+      </c>
+      <c r="D16" s="90" t="s">
         <v>2715</v>
       </c>
-      <c r="C16" s="89" t="s">
-        <v>2709</v>
-      </c>
-      <c r="D16" s="90" t="s">
-        <v>2710</v>
-      </c>
       <c r="E16" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44657,16 +44334,16 @@
         <v>2014</v>
       </c>
       <c r="B18" s="89" t="s">
-        <v>2719</v>
+        <v>2724</v>
       </c>
       <c r="C18" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D18" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W18" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44674,16 +44351,16 @@
         <v>2031</v>
       </c>
       <c r="B19" s="89" t="s">
-        <v>2720</v>
+        <v>2725</v>
       </c>
       <c r="C19" s="89" t="s">
-        <v>2716</v>
+        <v>2721</v>
       </c>
       <c r="D19" s="90" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="W19" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44691,16 +44368,16 @@
         <v>2047</v>
       </c>
       <c r="B20" s="89" t="s">
-        <v>2721</v>
+        <v>2726</v>
       </c>
       <c r="C20" s="89" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="D20" s="90" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="W20" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44708,19 +44385,19 @@
         <v>2062</v>
       </c>
       <c r="B21" s="89" t="s">
-        <v>2722</v>
+        <v>2727</v>
       </c>
       <c r="C21" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D21" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E21" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W21" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44728,40 +44405,40 @@
         <v>2075</v>
       </c>
       <c r="E22" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F22" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="G22" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I22" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="J22" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="K22" s="89" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="M22" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N22" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="P22" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="S22" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="T22" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="U22" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44769,19 +44446,19 @@
         <v>2087</v>
       </c>
       <c r="B23" s="89" t="s">
+        <v>2719</v>
+      </c>
+      <c r="C23" s="89" t="s">
         <v>2714</v>
       </c>
-      <c r="C23" s="89" t="s">
-        <v>2709</v>
-      </c>
       <c r="D23" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E23" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W23" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44789,64 +44466,64 @@
         <v>2103</v>
       </c>
       <c r="B24" s="89" t="s">
-        <v>2723</v>
+        <v>2728</v>
       </c>
       <c r="C24" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D24" s="90" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="E24" s="89" t="s">
-        <v>2724</v>
+        <v>2729</v>
       </c>
       <c r="F24" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G24" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="I24" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J24" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K24" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M24" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N24" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="O24" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="P24" s="90" t="s">
-        <v>2725</v>
+        <v>2730</v>
       </c>
       <c r="Q24" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="S24" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="T24" s="89" t="s">
-        <v>2725</v>
+        <v>2730</v>
       </c>
       <c r="U24" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="X24" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Y24" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Z24" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44854,37 +44531,37 @@
         <v>481</v>
       </c>
       <c r="B25" s="89" t="s">
-        <v>2712</v>
+        <v>2717</v>
       </c>
       <c r="C25" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D25" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E25" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="J25" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="K25" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M25" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N25" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q25" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U25" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W25" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44892,46 +44569,46 @@
         <v>2192</v>
       </c>
       <c r="B26" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="C26" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D26" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E26" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F26" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G26" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="I26" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J26" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K26" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M26" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N26" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="P26" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q26" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U26" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44939,28 +44616,28 @@
         <v>2214</v>
       </c>
       <c r="B27" s="89" t="s">
-        <v>2724</v>
+        <v>2729</v>
       </c>
       <c r="C27" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="D27" s="90" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="E27" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="H27" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J27" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K27" s="89" t="s">
-        <v>2717</v>
+        <v>2722</v>
       </c>
       <c r="N27" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -44968,52 +44645,52 @@
         <v>2232</v>
       </c>
       <c r="B28" s="89" t="s">
-        <v>2726</v>
+        <v>2731</v>
       </c>
       <c r="C28" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D28" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K28" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M28" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="O28" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Q28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U28" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="X28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Y28" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Z28" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45021,37 +44698,37 @@
         <v>2297</v>
       </c>
       <c r="B29" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C29" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D29" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E29" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="G29" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="I29" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J29" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K29" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="N29" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q29" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U29" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45059,40 +44736,40 @@
         <v>2317</v>
       </c>
       <c r="B30" s="89" t="s">
-        <v>2712</v>
+        <v>2717</v>
       </c>
       <c r="C30" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D30" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E30" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F30" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G30" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I30" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J30" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="K30" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="N30" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q30" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="W30" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45100,10 +44777,10 @@
         <v>1679</v>
       </c>
       <c r="B31" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C31" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45111,55 +44788,55 @@
         <v>1680</v>
       </c>
       <c r="B32" s="89" t="s">
-        <v>2727</v>
+        <v>2732</v>
       </c>
       <c r="C32" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D32" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E32" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F32" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I32" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J32" s="89" t="s">
-        <v>2728</v>
+        <v>2733</v>
       </c>
       <c r="K32" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M32" s="90" t="s">
-        <v>2716</v>
+        <v>2721</v>
       </c>
       <c r="N32" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="O32" s="89" t="s">
-        <v>2729</v>
+        <v>2734</v>
       </c>
       <c r="P32" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q32" s="89" t="s">
-        <v>2716</v>
+        <v>2721</v>
       </c>
       <c r="U32" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W32" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="X32" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Z32" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45167,25 +44844,25 @@
         <v>1681</v>
       </c>
       <c r="B33" s="89" t="s">
-        <v>2712</v>
+        <v>2717</v>
       </c>
       <c r="C33" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="D33" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E33" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J33" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K33" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="N33" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45193,30 +44870,30 @@
         <v>2367</v>
       </c>
       <c r="B34" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="C34" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D34" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E34" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I34" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K34" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="N34" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="89" t="s">
-        <v>2730</v>
+        <v>2735</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45224,13 +44901,13 @@
         <v>2392</v>
       </c>
       <c r="B36" s="89" t="s">
-        <v>2731</v>
+        <v>2736</v>
       </c>
       <c r="C36" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="D36" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45238,10 +44915,10 @@
         <v>2407</v>
       </c>
       <c r="B37" s="89" t="s">
-        <v>2732</v>
+        <v>2737</v>
       </c>
       <c r="D37" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45254,66 +44931,66 @@
         <v>1682</v>
       </c>
       <c r="B39" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C39" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D39" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E39" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G39" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I39" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J39" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K39" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="N39" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="P39" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U39" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="V39" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W39" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="101" t="s">
-        <v>2733</v>
+        <v>2738</v>
       </c>
       <c r="B40" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C40" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="D40" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J40" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="R40" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W40" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45321,37 +44998,37 @@
         <v>2495</v>
       </c>
       <c r="B41" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C41" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D41" s="90" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="E41" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G41" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I41" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J41" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K41" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="N41" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q41" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="U41" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45359,64 +45036,64 @@
         <v>1684</v>
       </c>
       <c r="B42" s="89" t="s">
-        <v>2734</v>
+        <v>2739</v>
       </c>
       <c r="C42" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D42" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E42" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="F42" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="G42" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I42" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J42" s="89" t="s">
-        <v>2725</v>
+        <v>2730</v>
       </c>
       <c r="K42" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="M42" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N42" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="O42" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="P42" s="90" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="Q42" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="T42" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
       <c r="U42" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W42" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="X42" s="89" t="s">
-        <v>2735</v>
+        <v>2740</v>
       </c>
       <c r="Y42" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Z42" s="89" t="s">
-        <v>2713</v>
+        <v>2718</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45424,34 +45101,34 @@
         <v>1685</v>
       </c>
       <c r="B43" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="C43" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D43" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E43" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="G43" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J43" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="K43" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="N43" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U43" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="V43" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45459,7 +45136,7 @@
         <v>2550</v>
       </c>
       <c r="B44" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -45467,45 +45144,45 @@
         <v>1676</v>
       </c>
       <c r="B45" s="89" t="s">
-        <v>2729</v>
+        <v>2734</v>
       </c>
       <c r="C45" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="D45" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="E45" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="I45" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="J45" s="89" t="s">
-        <v>2709</v>
+        <v>2714</v>
       </c>
       <c r="K45" s="89" t="s">
-        <v>2711</v>
+        <v>2716</v>
       </c>
       <c r="M45" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="N45" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="Q45" s="89" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="U45" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
       <c r="W45" s="90" t="s">
-        <v>2710</v>
+        <v>2715</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="129" t="s">
-        <v>2736</v>
+        <v>2741</v>
       </c>
       <c r="B55" s="129"/>
       <c r="C55" s="129"/>
@@ -45521,7 +45198,7 @@
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="129" t="s">
-        <v>2737</v>
+        <v>2742</v>
       </c>
       <c r="B56" s="129"/>
       <c r="C56" s="129"/>
@@ -45536,7 +45213,7 @@
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="129" t="s">
-        <v>2738</v>
+        <v>2743</v>
       </c>
       <c r="B57" s="129"/>
       <c r="C57" s="129"/>
@@ -45551,7 +45228,7 @@
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="129" t="s">
-        <v>2739</v>
+        <v>2744</v>
       </c>
       <c r="B58" s="129"/>
       <c r="C58" s="129"/>
